--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -2276,11 +2276,11 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>48908.37</v>
+        <v>49741.82</v>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F25" s="20">
@@ -2296,7 +2296,7 @@
         <v/>
       </c>
       <c r="I25" s="13" t="n">
-        <v>48908.37</v>
+        <v>49741.82</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
@@ -2316,11 +2316,11 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>10963.58</v>
+        <v>12003.52</v>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F26" s="20">
@@ -2336,7 +2336,7 @@
         <v/>
       </c>
       <c r="I26" s="13" t="n">
-        <v>10963.58</v>
+        <v>12003.52</v>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
@@ -2356,11 +2356,11 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>12658.36</v>
+        <v>13847.2</v>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F27" s="20">
@@ -2376,7 +2376,7 @@
         <v/>
       </c>
       <c r="I27" s="13" t="n">
-        <v>12658.36</v>
+        <v>13847.2</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -2396,11 +2396,11 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>5460.08</v>
+        <v>5280.06</v>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F28" s="20">
@@ -2416,7 +2416,7 @@
         <v/>
       </c>
       <c r="I28" s="13" t="n">
-        <v>5460.08</v>
+        <v>5280.06</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
@@ -2436,11 +2436,11 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>7356.08</v>
+        <v>7048.52</v>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F29" s="20">
@@ -2456,7 +2456,7 @@
         <v/>
       </c>
       <c r="I29" s="13" t="n">
-        <v>7356.08</v>
+        <v>7048.52</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
@@ -2476,11 +2476,11 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1670.19</v>
+        <v>1709.76</v>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F30" s="20">
@@ -2496,7 +2496,7 @@
         <v/>
       </c>
       <c r="I30" s="13" t="n">
-        <v>1670.19</v>
+        <v>1709.76</v>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
@@ -2516,11 +2516,11 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>59651.77</v>
+        <v>53225.97</v>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F31" s="20">
@@ -2536,7 +2536,7 @@
         <v/>
       </c>
       <c r="I31" s="13" t="n">
-        <v>59651.77</v>
+        <v>53225.97</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -2556,11 +2556,11 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>2327.86</v>
+        <v>2640.66</v>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F32" s="20">
@@ -2576,7 +2576,7 @@
         <v/>
       </c>
       <c r="I32" s="13" t="n">
-        <v>2327.86</v>
+        <v>2640.66</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -2596,11 +2596,11 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>243.05</v>
+        <v>223.96</v>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F33" s="20">
@@ -2616,7 +2616,7 @@
         <v/>
       </c>
       <c r="I33" s="13" t="n">
-        <v>243.05</v>
+        <v>223.96</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
@@ -2636,11 +2636,11 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>79.31999999999999</v>
+        <v>84.91</v>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F34" s="20">
@@ -2656,7 +2656,7 @@
         <v/>
       </c>
       <c r="I34" s="13" t="n">
-        <v>79.31999999999999</v>
+        <v>84.91</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
@@ -2676,11 +2676,11 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>309.53</v>
+        <v>290.5</v>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F35" s="20">
@@ -2696,7 +2696,7 @@
         <v/>
       </c>
       <c r="I35" s="13" t="n">
-        <v>309.53</v>
+        <v>290.5</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
@@ -2716,11 +2716,11 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>428.92</v>
+        <v>395.44</v>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F36" s="20">
@@ -2736,7 +2736,7 @@
         <v/>
       </c>
       <c r="I36" s="13" t="n">
-        <v>428.92</v>
+        <v>395.44</v>
       </c>
     </row>
     <row r="37" ht="14" customHeight="1">
@@ -2756,11 +2756,11 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>18.91</v>
+        <v>28.05</v>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F37" s="20">
@@ -2776,7 +2776,7 @@
         <v/>
       </c>
       <c r="I37" s="13" t="n">
-        <v>18.91</v>
+        <v>28.05</v>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
@@ -2796,11 +2796,11 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>30.18</v>
+        <v>39.41</v>
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F38" s="20">
@@ -2816,7 +2816,7 @@
         <v/>
       </c>
       <c r="I38" s="13" t="n">
-        <v>30.18</v>
+        <v>39.41</v>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1">
@@ -2836,11 +2836,11 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>44.96</v>
+        <v>88.59</v>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F39" s="20">
@@ -2856,7 +2856,7 @@
         <v/>
       </c>
       <c r="I39" s="13" t="n">
-        <v>44.96</v>
+        <v>88.59</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
@@ -2876,11 +2876,11 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>2121.73</v>
+        <v>1848.1</v>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F40" s="20">
@@ -2896,7 +2896,7 @@
         <v/>
       </c>
       <c r="I40" s="13" t="n">
-        <v>2121.73</v>
+        <v>1848.1</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
@@ -2916,11 +2916,11 @@
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>3089.16</v>
+        <v>2646.28</v>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F41" s="20">
@@ -2936,7 +2936,7 @@
         <v/>
       </c>
       <c r="I41" s="13" t="n">
-        <v>3089.16</v>
+        <v>2646.28</v>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
@@ -2956,11 +2956,11 @@
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>11812.61</v>
+        <v>9896.620000000001</v>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F42" s="20">
@@ -2976,7 +2976,7 @@
         <v/>
       </c>
       <c r="I42" s="13" t="n">
-        <v>11812.61</v>
+        <v>9896.620000000001</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
@@ -2996,11 +2996,11 @@
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>9640.309999999999</v>
+        <v>9265.620000000001</v>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F43" s="20">
@@ -3016,7 +3016,7 @@
         <v/>
       </c>
       <c r="I43" s="13" t="n">
-        <v>9640.309999999999</v>
+        <v>9265.620000000001</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
@@ -3036,11 +3036,11 @@
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>723278.66</v>
+        <v>576288.2</v>
       </c>
       <c r="E44" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F44" s="20">
@@ -3056,7 +3056,7 @@
         <v/>
       </c>
       <c r="I44" s="13" t="n">
-        <v>723278.66</v>
+        <v>576288.2</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
@@ -3076,11 +3076,11 @@
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>123273.35</v>
+        <v>99145.64999999999</v>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F45" s="20">
@@ -3096,7 +3096,7 @@
         <v/>
       </c>
       <c r="I45" s="13" t="n">
-        <v>123273.35</v>
+        <v>99145.64999999999</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
@@ -3116,11 +3116,11 @@
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>24136.06</v>
+        <v>20726.2</v>
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F46" s="20">
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="I46" s="13" t="n">
-        <v>24136.06</v>
+        <v>20726.2</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
@@ -3156,11 +3156,11 @@
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>660.4</v>
+        <v>572.8</v>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F47" s="20">
@@ -3176,7 +3176,7 @@
         <v/>
       </c>
       <c r="I47" s="13" t="n">
-        <v>660.4</v>
+        <v>572.8</v>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
@@ -3196,11 +3196,11 @@
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>179.47</v>
+        <v>185.85</v>
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,625</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F48" s="20">
@@ -3216,7 +3216,7 @@
         <v/>
       </c>
       <c r="I48" s="13" t="n">
-        <v>179.47</v>
+        <v>185.85</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -1536,7 +1536,7 @@
         <v/>
       </c>
       <c r="I6" s="13" t="n">
-        <v>62.35</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1576,7 +1576,7 @@
         <v/>
       </c>
       <c r="I7" s="13" t="n">
-        <v>71.84999999999999</v>
+        <v>60.35</v>
       </c>
     </row>
     <row r="8" ht="33" customHeight="1">
@@ -1616,7 +1616,7 @@
         <v/>
       </c>
       <c r="I8" s="13" t="n">
-        <v>3274.35</v>
+        <v>2750.45</v>
       </c>
     </row>
     <row r="9" ht="33" customHeight="1">
@@ -1656,7 +1656,7 @@
         <v/>
       </c>
       <c r="I9" s="13" t="n">
-        <v>3524.35</v>
+        <v>2960.45</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
@@ -1696,7 +1696,7 @@
         <v/>
       </c>
       <c r="I10" s="13" t="n">
-        <v>43987.5</v>
+        <v>36949.5</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -1736,7 +1736,7 @@
         <v/>
       </c>
       <c r="I11" s="13" t="n">
-        <v>46482.43</v>
+        <v>39045.24</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -1776,7 +1776,7 @@
         <v/>
       </c>
       <c r="I12" s="13" t="n">
-        <v>44681.18</v>
+        <v>37532.19</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -1816,7 +1816,7 @@
         <v/>
       </c>
       <c r="I13" s="13" t="n">
-        <v>85943.50999999999</v>
+        <v>72192.55</v>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
@@ -1856,7 +1856,7 @@
         <v/>
       </c>
       <c r="I14" s="13" t="n">
-        <v>1028.33</v>
+        <v>863.8</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1896,7 +1896,7 @@
         <v/>
       </c>
       <c r="I15" s="13" t="n">
-        <v>723.73</v>
+        <v>607.9299999999999</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1936,7 +1936,7 @@
         <v/>
       </c>
       <c r="I16" s="13" t="n">
-        <v>1106.28</v>
+        <v>929.28</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1976,7 +1976,7 @@
         <v/>
       </c>
       <c r="I17" s="13" t="n">
-        <v>2116.1</v>
+        <v>1777.52</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
@@ -2016,7 +2016,7 @@
         <v/>
       </c>
       <c r="I18" s="13" t="n">
-        <v>443.51</v>
+        <v>372.55</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2056,7 +2056,7 @@
         <v/>
       </c>
       <c r="I19" s="13" t="n">
-        <v>454.16</v>
+        <v>381.49</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -2096,7 +2096,7 @@
         <v/>
       </c>
       <c r="I20" s="13" t="n">
-        <v>296.13</v>
+        <v>248.75</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -2136,7 +2136,7 @@
         <v/>
       </c>
       <c r="I21" s="13" t="n">
-        <v>386.03</v>
+        <v>324.27</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -2176,7 +2176,7 @@
         <v/>
       </c>
       <c r="I22" s="13" t="n">
-        <v>218.54</v>
+        <v>183.57</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -2216,7 +2216,7 @@
         <v/>
       </c>
       <c r="I23" s="13" t="n">
-        <v>175.8</v>
+        <v>147.67</v>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
@@ -2256,7 +2256,7 @@
         <v/>
       </c>
       <c r="I24" s="13" t="n">
-        <v>4457.5</v>
+        <v>3744.3</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -2296,7 +2296,7 @@
         <v/>
       </c>
       <c r="I25" s="13" t="n">
-        <v>49741.82</v>
+        <v>41783.13</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
@@ -2336,7 +2336,7 @@
         <v/>
       </c>
       <c r="I26" s="13" t="n">
-        <v>12003.52</v>
+        <v>10082.96</v>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
@@ -2376,7 +2376,7 @@
         <v/>
       </c>
       <c r="I27" s="13" t="n">
-        <v>13847.2</v>
+        <v>11631.65</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -2416,7 +2416,7 @@
         <v/>
       </c>
       <c r="I28" s="13" t="n">
-        <v>5280.06</v>
+        <v>4435.25</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
@@ -2456,7 +2456,7 @@
         <v/>
       </c>
       <c r="I29" s="13" t="n">
-        <v>7048.52</v>
+        <v>5920.76</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
@@ -2496,7 +2496,7 @@
         <v/>
       </c>
       <c r="I30" s="13" t="n">
-        <v>1709.76</v>
+        <v>1436.2</v>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
@@ -2536,7 +2536,7 @@
         <v/>
       </c>
       <c r="I31" s="13" t="n">
-        <v>53225.97</v>
+        <v>44709.81</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -2576,7 +2576,7 @@
         <v/>
       </c>
       <c r="I32" s="13" t="n">
-        <v>2640.66</v>
+        <v>2218.15</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -2616,7 +2616,7 @@
         <v/>
       </c>
       <c r="I33" s="13" t="n">
-        <v>223.96</v>
+        <v>188.13</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
@@ -2656,7 +2656,7 @@
         <v/>
       </c>
       <c r="I34" s="13" t="n">
-        <v>84.91</v>
+        <v>71.31999999999999</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
@@ -2696,7 +2696,7 @@
         <v/>
       </c>
       <c r="I35" s="13" t="n">
-        <v>290.5</v>
+        <v>244.02</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
@@ -2736,7 +2736,7 @@
         <v/>
       </c>
       <c r="I36" s="13" t="n">
-        <v>395.44</v>
+        <v>332.17</v>
       </c>
     </row>
     <row r="37" ht="14" customHeight="1">
@@ -2776,7 +2776,7 @@
         <v/>
       </c>
       <c r="I37" s="13" t="n">
-        <v>28.05</v>
+        <v>23.56</v>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
@@ -2816,7 +2816,7 @@
         <v/>
       </c>
       <c r="I38" s="13" t="n">
-        <v>39.41</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1">
@@ -2856,7 +2856,7 @@
         <v/>
       </c>
       <c r="I39" s="13" t="n">
-        <v>88.59</v>
+        <v>74.42</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
@@ -2896,7 +2896,7 @@
         <v/>
       </c>
       <c r="I40" s="13" t="n">
-        <v>1848.1</v>
+        <v>1552.4</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
@@ -2936,7 +2936,7 @@
         <v/>
       </c>
       <c r="I41" s="13" t="n">
-        <v>2646.28</v>
+        <v>2222.88</v>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
@@ -2976,7 +2976,7 @@
         <v/>
       </c>
       <c r="I42" s="13" t="n">
-        <v>9896.620000000001</v>
+        <v>8313.16</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
@@ -3016,7 +3016,7 @@
         <v/>
       </c>
       <c r="I43" s="13" t="n">
-        <v>9265.620000000001</v>
+        <v>7783.12</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
@@ -3056,7 +3056,7 @@
         <v/>
       </c>
       <c r="I44" s="13" t="n">
-        <v>576288.2</v>
+        <v>484082.09</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
@@ -3096,7 +3096,7 @@
         <v/>
       </c>
       <c r="I45" s="13" t="n">
-        <v>99145.64999999999</v>
+        <v>83282.35000000001</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="I46" s="13" t="n">
-        <v>20726.2</v>
+        <v>17410.01</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
@@ -3176,7 +3176,7 @@
         <v/>
       </c>
       <c r="I47" s="13" t="n">
-        <v>572.8</v>
+        <v>481.15</v>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
@@ -3216,7 +3216,7 @@
         <v/>
       </c>
       <c r="I48" s="13" t="n">
-        <v>185.85</v>
+        <v>156.11</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
@@ -3256,7 +3256,7 @@
         <v/>
       </c>
       <c r="I49" s="13" t="n">
-        <v>393.69</v>
+        <v>330.7</v>
       </c>
     </row>
     <row r="50" ht="33" customHeight="1">
@@ -3296,7 +3296,7 @@
         <v/>
       </c>
       <c r="I50" s="13" t="n">
-        <v>1624.67</v>
+        <v>1364.72</v>
       </c>
     </row>
     <row r="51" ht="14" customHeight="1">
@@ -3336,7 +3336,7 @@
         <v/>
       </c>
       <c r="I51" s="13" t="n">
-        <v>1120.05</v>
+        <v>940.84</v>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
@@ -3376,7 +3376,7 @@
         <v/>
       </c>
       <c r="I52" s="13" t="n">
-        <v>271.25</v>
+        <v>227.85</v>
       </c>
     </row>
     <row r="53" ht="33" customHeight="1">
@@ -3416,7 +3416,7 @@
         <v/>
       </c>
       <c r="I53" s="13" t="n">
-        <v>1035.88</v>
+        <v>870.14</v>
       </c>
     </row>
     <row r="54" ht="33" customHeight="1">
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="I54" s="13" t="n">
-        <v>3199.68</v>
+        <v>2687.73</v>
       </c>
     </row>
     <row r="55" ht="44" customHeight="1">
@@ -3496,7 +3496,7 @@
         <v/>
       </c>
       <c r="I55" s="13" t="n">
-        <v>835.1</v>
+        <v>701.48</v>
       </c>
     </row>
   </sheetData>

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -827,13 +827,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Bu keşif özeti yalnızca bu yapıya aittir. TKDK'ya sunulacak nüshada F ve G sütunları (birim fiyat ve tutar) gizlenmelidir; keşif özetinde fiyat sütunu bulunmaz.</t>
-        </is>
-      </c>
-    </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -1380,12 +1373,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A13:A21"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A11:A12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1422,7 +1414,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Sarı hücreler değiştirilebilir. Fiyatlar keşif özetinin birimine göredir (dönüşümlü pozlarda ör. TL/kg, TL/m²) ve KDV hariçtir. Keşif özetinin TKDK'ya sunulan nüshasında fiyat sütunu bulunmaz; bu sekme kendi maliyet takibiniz içindir.</t>
+          <t>Sarı hücreler değiştirilebilir. Fiyatlar keşif özetinin birimine göredir (dönüşümlü pozlarda ör. TL/kg, TL/m²) ve KDV hariçtir.</t>
         </is>
       </c>
     </row>
@@ -3540,13 +3532,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Bu keşif özeti yalnızca bu yapıya aittir. TKDK'ya sunulacak nüshada F ve G sütunları (birim fiyat ve tutar) gizlenmelidir; keşif özetinde fiyat sütunu bulunmaz.</t>
-        </is>
-      </c>
-    </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -4788,12 +4773,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
@@ -4837,13 +4821,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Bu keşif özeti yalnızca bu yapıya aittir. TKDK'ya sunulacak nüshada F ve G sütunları (birim fiyat ve tutar) gizlenmelidir; keşif özetinde fiyat sütunu bulunmaz.</t>
-        </is>
-      </c>
-    </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -6085,12 +6062,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
@@ -6134,13 +6110,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Bu keşif özeti yalnızca bu yapıya aittir. TKDK'ya sunulacak nüshada F ve G sütunları (birim fiyat ve tutar) gizlenmelidir; keşif özetinde fiyat sütunu bulunmaz.</t>
-        </is>
-      </c>
-    </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -6389,9 +6358,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A3:G3"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -6431,13 +6399,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Bu keşif özeti yalnızca bu yapıya aittir. TKDK'ya sunulacak nüshada F ve G sütunları (birim fiyat ve tutar) gizlenmelidir; keşif özetinde fiyat sütunu bulunmaz.</t>
-        </is>
-      </c>
-    </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -6657,8 +6618,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:G3"/>
+  <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -6698,13 +6658,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Bu keşif özeti yalnızca bu yapıya aittir. TKDK'ya sunulacak nüshada F ve G sütunları (birim fiyat ve tutar) gizlenmelidir; keşif özetinde fiyat sütunu bulunmaz.</t>
-        </is>
-      </c>
-    </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -6924,8 +6877,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:G3"/>
+  <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -6965,13 +6917,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Bu keşif özeti yalnızca bu yapıya aittir. TKDK'ya sunulacak nüshada F ve G sütunları (birim fiyat ve tutar) gizlenmelidir; keşif özetinde fiyat sütunu bulunmaz.</t>
-        </is>
-      </c>
-    </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -7191,8 +7136,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:G3"/>
+  <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -7232,13 +7176,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Bu keşif özeti yalnızca bu yapıya aittir. TKDK'ya sunulacak nüshada F ve G sütunları (birim fiyat ve tutar) gizlenmelidir; keşif özetinde fiyat sütunu bulunmaz.</t>
-        </is>
-      </c>
-    </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -7458,8 +7395,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:G3"/>
+  <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -11,12 +11,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fiyatlar" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Kümes A Blok" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Kümes B Blok" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Gübre Çukuru" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 Ölü Atma Çukuru" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 Foseptik" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Yem Silosu Betonarme Kaidele" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Su Deposu" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Çevre Düzenlemesi ve Saha Al" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -550,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -600,11 +594,11 @@
         </is>
       </c>
       <c r="C4" s="5">
-        <f>'01 Kümes A Blok'!$G$45</f>
+        <f>'01 Kümes A Blok'!$G$43</f>
         <v/>
       </c>
       <c r="D4" s="6">
-        <f>C4/$C$12</f>
+        <f>C4/$C$6</f>
         <v/>
       </c>
     </row>
@@ -620,764 +614,56 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>'02 Kümes B Blok'!$G$45</f>
+        <f>'02 Kümes B Blok'!$G$43</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>C5/$C$12</f>
+        <f>C5/$C$6</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Gübre Çukuru</t>
-        </is>
-      </c>
-      <c r="C6" s="5">
-        <f>'03 Gübre Çukuru'!$G$12</f>
-        <v/>
-      </c>
-      <c r="D6" s="6">
-        <f>C6/$C$12</f>
-        <v/>
-      </c>
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>ARA TOPLAM (KDV hariç)</t>
+        </is>
+      </c>
+      <c r="C6" s="9">
+        <f>SUM(C4:C5)</f>
+        <v/>
+      </c>
+      <c r="D6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Ölü Atma Çukuru</t>
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>KDV</t>
         </is>
       </c>
       <c r="C7" s="5">
-        <f>'04 Ölü Atma Çukuru'!$G$11</f>
-        <v/>
-      </c>
-      <c r="D7" s="6">
-        <f>C7/$C$12</f>
-        <v/>
-      </c>
+        <f>C6*'Fiyatlar'!$F$3</f>
+        <v/>
+      </c>
+      <c r="D7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Foseptik</t>
-        </is>
-      </c>
-      <c r="C8" s="5">
-        <f>'05 Foseptik'!$G$11</f>
-        <v/>
-      </c>
-      <c r="D8" s="6">
-        <f>C8/$C$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Yem Silosu Betonarme Kaideleri</t>
-        </is>
-      </c>
-      <c r="C9" s="5">
-        <f>'06 Yem Silosu Betonarme Kaidele'!$G$11</f>
-        <v/>
-      </c>
-      <c r="D9" s="6">
-        <f>C9/$C$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Su Deposu</t>
-        </is>
-      </c>
-      <c r="C10" s="5">
-        <f>'07 Su Deposu'!$G$11</f>
-        <v/>
-      </c>
-      <c r="D10" s="6">
-        <f>C10/$C$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C11" s="5">
-        <f>'08 Çevre Düzenlemesi ve Saha Al'!$G$22</f>
-        <v/>
-      </c>
-      <c r="D11" s="6">
-        <f>C11/$C$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>ARA TOPLAM (KDV hariç)</t>
-        </is>
-      </c>
-      <c r="C12" s="9">
-        <f>SUM(C4:C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>KDV</t>
-        </is>
-      </c>
-      <c r="C13" s="5">
-        <f>C12*'Fiyatlar'!$F$3</f>
-        <v/>
-      </c>
-      <c r="D13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>GENEL TOPLAM (KDV dâhil)</t>
         </is>
       </c>
-      <c r="C14" s="13">
-        <f>C12+C13</f>
-        <v/>
-      </c>
-      <c r="D14" s="11" t="n"/>
+      <c r="C8" s="13">
+        <f>C6+C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KEŞİF ÖZETİ — ÇEVRE DÜZENLEMESI VE SAHA ALTYAPISI</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Musab Eder Çiftliği — Kocaeli / Karamürsel / İnebeyli Mah., 138 ada 17 parsel</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>EK-1 uygun harcama kalemi</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Yapım işinin adı</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Miktar</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Birim fiyat (TL)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Tutar (TL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>15.120.1001</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>Makine ile yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="n">
-        <v>260.9425</v>
-      </c>
-      <c r="F6" s="24">
-        <f>IFERROR(VLOOKUP($B6,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="5">
-        <f>E6*F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="n">
-        <v>1.566</v>
-      </c>
-      <c r="F7" s="24">
-        <f>IFERROR(VLOOKUP($B7,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="5">
-        <f>E7*F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="F8" s="24">
-        <f>IFERROR(VLOOKUP($B8,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="5">
-        <f>E8*F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="n">
-        <v>0.1409</v>
-      </c>
-      <c r="F9" s="24">
-        <f>IFERROR(VLOOKUP($B9,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="5">
-        <f>E9*F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>Çevre düzenlemesi ve çit işleri</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>TKDK-0091</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="n">
-        <v>361.04</v>
-      </c>
-      <c r="F10" s="24">
-        <f>IFERROR(VLOOKUP($B10,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="5">
-        <f>E10*F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>Kanalizasyon işleri</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>43.527.1001</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" s="24">
-        <f>IFERROR(VLOOKUP($B11,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="5">
-        <f>E11*F11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="26" t="n"/>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>15.560.1003</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="24">
-        <f>IFERROR(VLOOKUP($B12,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G12" s="5">
-        <f>E12*F12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>30.100.1104</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="24">
-        <f>IFERROR(VLOOKUP($B13,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G13" s="5">
-        <f>E13*F13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="25" t="n"/>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>30.100.2106</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="24">
-        <f>IFERROR(VLOOKUP($B14,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G14" s="5">
-        <f>E14*F14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="25" t="n"/>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>30.135.3201</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="24">
-        <f>IFERROR(VLOOKUP($B15,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G15" s="5">
-        <f>E15*F15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="14" customHeight="1">
-      <c r="A16" s="25" t="n"/>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>30.110.1104</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="24">
-        <f>IFERROR(VLOOKUP($B16,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G16" s="5">
-        <f>E16*F16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="25" t="n"/>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>30.115.1003</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="24">
-        <f>IFERROR(VLOOKUP($B17,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G17" s="5">
-        <f>E17*F17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="14" customHeight="1">
-      <c r="A18" s="25" t="n"/>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>30.140.3105</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="n">
-        <v>50</v>
-      </c>
-      <c r="F18" s="24">
-        <f>IFERROR(VLOOKUP($B18,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G18" s="5">
-        <f>E18*F18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="14" customHeight="1">
-      <c r="A19" s="25" t="n"/>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>30.140.3101</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E19" s="23" t="n">
-        <v>50</v>
-      </c>
-      <c r="F19" s="24">
-        <f>IFERROR(VLOOKUP($B19,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G19" s="5">
-        <f>E19*F19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="14" customHeight="1">
-      <c r="A20" s="25" t="n"/>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>30.172.1706</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="F20" s="24">
-        <f>IFERROR(VLOOKUP($B20,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G20" s="5">
-        <f>E20*F20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="14" customHeight="1">
-      <c r="A21" s="26" t="n"/>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>30.170.4002</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>LED projektör, ışık akısı en az 5100 lm</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" s="24">
-        <f>IFERROR(VLOOKUP($B21,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G21" s="5">
-        <f>E21*F21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="27" t="inlineStr">
-        <is>
-          <t>TOPLAM (KDV hariç)</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="13">
-        <f>SUM(G6:G21)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A13:A21"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1390,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1531,15 +817,15 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
+    <row r="7" ht="33" customHeight="1">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>15.120.1101</t>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1548,7 +834,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>71.84999999999999</v>
+        <v>3274.35</v>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
@@ -1568,18 +854,18 @@
         <v/>
       </c>
       <c r="I7" s="13" t="n">
-        <v>60.35</v>
+        <v>2750.45</v>
       </c>
     </row>
     <row r="8" ht="33" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>15.150.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1588,7 +874,7 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3274.35</v>
+        <v>3524.35</v>
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
@@ -1608,27 +894,27 @@
         <v/>
       </c>
       <c r="I8" s="13" t="n">
-        <v>2750.45</v>
-      </c>
-    </row>
-    <row r="9" ht="33" customHeight="1">
+        <v>2960.45</v>
+      </c>
+    </row>
+    <row r="9" ht="14" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.160.1002</t>
         </is>
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Nervürlü çelik hasırın yerine konulması</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>3524.35</v>
+        <v>43987.5</v>
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
@@ -1648,18 +934,18 @@
         <v/>
       </c>
       <c r="I9" s="13" t="n">
-        <v>2960.45</v>
-      </c>
-    </row>
-    <row r="10" ht="14" customHeight="1">
+        <v>36949.5</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>15.160.1002</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>Nervürlü çelik hasırın yerine konulması</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1668,7 +954,7 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>43987.5</v>
+        <v>46482.43</v>
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
@@ -1688,18 +974,18 @@
         <v/>
       </c>
       <c r="I10" s="13" t="n">
-        <v>36949.5</v>
+        <v>39045.24</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1708,7 +994,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>46482.43</v>
+        <v>44681.18</v>
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
@@ -1728,18 +1014,18 @@
         <v/>
       </c>
       <c r="I11" s="13" t="n">
-        <v>39045.24</v>
+        <v>37532.19</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1748,7 +1034,7 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>44681.18</v>
+        <v>85943.50999999999</v>
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
@@ -1768,27 +1054,27 @@
         <v/>
       </c>
       <c r="I12" s="13" t="n">
-        <v>37532.19</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
+        <v>72192.55</v>
+      </c>
+    </row>
+    <row r="13" ht="14" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>15.165.1003</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>85943.50999999999</v>
+        <v>1028.33</v>
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
@@ -1808,18 +1094,18 @@
         <v/>
       </c>
       <c r="I13" s="13" t="n">
-        <v>72192.55</v>
-      </c>
-    </row>
-    <row r="14" ht="14" customHeight="1">
+        <v>863.8</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1828,7 +1114,7 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1028.33</v>
+        <v>723.73</v>
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
@@ -1848,18 +1134,18 @@
         <v/>
       </c>
       <c r="I14" s="13" t="n">
-        <v>863.8</v>
+        <v>607.9299999999999</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1868,7 +1154,7 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>723.73</v>
+        <v>1106.28</v>
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
@@ -1888,18 +1174,18 @@
         <v/>
       </c>
       <c r="I15" s="13" t="n">
-        <v>607.9299999999999</v>
+        <v>929.28</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1908,7 +1194,7 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1106.28</v>
+        <v>2116.1</v>
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
@@ -1928,18 +1214,18 @@
         <v/>
       </c>
       <c r="I16" s="13" t="n">
-        <v>929.28</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
+        <v>1777.52</v>
+      </c>
+    </row>
+    <row r="17" ht="14" customHeight="1">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1948,7 +1234,7 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2116.1</v>
+        <v>443.51</v>
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
@@ -1968,18 +1254,18 @@
         <v/>
       </c>
       <c r="I17" s="13" t="n">
-        <v>1777.52</v>
-      </c>
-    </row>
-    <row r="18" ht="14" customHeight="1">
+        <v>372.55</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1988,7 +1274,7 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>443.51</v>
+        <v>454.16</v>
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
@@ -2008,18 +1294,18 @@
         <v/>
       </c>
       <c r="I18" s="13" t="n">
-        <v>372.55</v>
+        <v>381.49</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2028,7 +1314,7 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>454.16</v>
+        <v>296.13</v>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
@@ -2048,18 +1334,18 @@
         <v/>
       </c>
       <c r="I19" s="13" t="n">
-        <v>381.49</v>
+        <v>248.75</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2068,7 +1354,7 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>296.13</v>
+        <v>386.03</v>
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
@@ -2088,27 +1374,27 @@
         <v/>
       </c>
       <c r="I20" s="13" t="n">
-        <v>248.75</v>
+        <v>324.27</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>386.03</v>
+        <v>218.54</v>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
@@ -2128,18 +1414,18 @@
         <v/>
       </c>
       <c r="I21" s="13" t="n">
-        <v>324.27</v>
+        <v>183.57</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2148,7 +1434,7 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>218.54</v>
+        <v>175.8</v>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
@@ -2168,31 +1454,31 @@
         <v/>
       </c>
       <c r="I22" s="13" t="n">
-        <v>183.57</v>
+        <v>147.67</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>30.100.2105</t>
         </is>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>175.8</v>
+        <v>12003.52</v>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 birim fiyat kitabı</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F23" s="20">
@@ -2208,18 +1494,18 @@
         <v/>
       </c>
       <c r="I23" s="13" t="n">
-        <v>147.67</v>
-      </c>
-    </row>
-    <row r="24" ht="14" customHeight="1">
+        <v>10082.96</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>15.560.1003</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2228,11 +1514,11 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>4457.5</v>
+        <v>5280.06</v>
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 birim fiyat kitabı</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
         </is>
       </c>
       <c r="F24" s="20">
@@ -2248,18 +1534,18 @@
         <v/>
       </c>
       <c r="I24" s="13" t="n">
-        <v>3744.3</v>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
+        <v>4435.25</v>
+      </c>
+    </row>
+    <row r="25" ht="14" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
         <is>
-          <t>30.100.1104</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2268,7 +1554,7 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>49741.82</v>
+        <v>1709.76</v>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
@@ -2288,27 +1574,27 @@
         <v/>
       </c>
       <c r="I25" s="13" t="n">
-        <v>41783.13</v>
+        <v>1436.2</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>12003.52</v>
+        <v>223.96</v>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
@@ -2328,27 +1614,27 @@
         <v/>
       </c>
       <c r="I26" s="13" t="n">
-        <v>10082.96</v>
-      </c>
-    </row>
-    <row r="27" ht="14" customHeight="1">
+        <v>188.13</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>30.100.2106</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>13847.2</v>
+        <v>290.5</v>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
@@ -2368,27 +1654,27 @@
         <v/>
       </c>
       <c r="I27" s="13" t="n">
-        <v>11631.65</v>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
+        <v>244.02</v>
+      </c>
+    </row>
+    <row r="28" ht="14" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>5280.06</v>
+        <v>28.05</v>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
@@ -2408,27 +1694,27 @@
         <v/>
       </c>
       <c r="I28" s="13" t="n">
-        <v>4435.25</v>
+        <v>23.56</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>30.110.1104</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>7048.52</v>
+        <v>39.41</v>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
@@ -2448,27 +1734,27 @@
         <v/>
       </c>
       <c r="I29" s="13" t="n">
-        <v>5920.76</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1709.76</v>
+        <v>88.59</v>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
@@ -2488,18 +1774,18 @@
         <v/>
       </c>
       <c r="I30" s="13" t="n">
-        <v>1436.2</v>
-      </c>
-    </row>
-    <row r="31" ht="14" customHeight="1">
+        <v>74.42</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>30.120.2016</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2508,7 +1794,7 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>53225.97</v>
+        <v>1848.1</v>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
@@ -2528,18 +1814,18 @@
         <v/>
       </c>
       <c r="I31" s="13" t="n">
-        <v>44709.81</v>
+        <v>1552.4</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>30.135.3201</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2548,7 +1834,7 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>2640.66</v>
+        <v>2646.28</v>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
@@ -2568,27 +1854,27 @@
         <v/>
       </c>
       <c r="I32" s="13" t="n">
-        <v>2218.15</v>
+        <v>2222.88</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>223.96</v>
+        <v>576288.2</v>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
@@ -2608,27 +1894,27 @@
         <v/>
       </c>
       <c r="I33" s="13" t="n">
-        <v>188.13</v>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
+        <v>484082.09</v>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>30.140.3101</t>
+          <t>30.740.5406</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>84.91</v>
+        <v>99145.64999999999</v>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
@@ -2648,27 +1934,27 @@
         <v/>
       </c>
       <c r="I34" s="13" t="n">
-        <v>71.31999999999999</v>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
+        <v>83282.35000000001</v>
+      </c>
+    </row>
+    <row r="35" ht="14" customHeight="1">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>290.5</v>
+        <v>20726.2</v>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
@@ -2688,18 +1974,18 @@
         <v/>
       </c>
       <c r="I35" s="13" t="n">
-        <v>244.02</v>
+        <v>17410.01</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>30.140.3105</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2708,7 +1994,7 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>395.44</v>
+        <v>572.8</v>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
@@ -2728,18 +2014,18 @@
         <v/>
       </c>
       <c r="I36" s="13" t="n">
-        <v>332.17</v>
-      </c>
-    </row>
-    <row r="37" ht="14" customHeight="1">
+        <v>481.15</v>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2748,7 +2034,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>28.05</v>
+        <v>185.85</v>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
@@ -2768,18 +2054,18 @@
         <v/>
       </c>
       <c r="I37" s="13" t="n">
-        <v>23.56</v>
-      </c>
-    </row>
-    <row r="38" ht="14" customHeight="1">
+        <v>156.11</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2788,11 +2074,11 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>39.41</v>
+        <v>393.69</v>
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F38" s="20">
@@ -2808,31 +2094,31 @@
         <v/>
       </c>
       <c r="I38" s="13" t="n">
-        <v>33.1</v>
+        <v>330.7</v>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>88.59</v>
+        <v>271.25</v>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F39" s="20">
@@ -2848,31 +2134,31 @@
         <v/>
       </c>
       <c r="I39" s="13" t="n">
-        <v>74.42</v>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
+        <v>227.85</v>
+      </c>
+    </row>
+    <row r="40" ht="33" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1848.1</v>
+        <v>1035.88</v>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F40" s="20">
@@ -2888,31 +2174,31 @@
         <v/>
       </c>
       <c r="I40" s="13" t="n">
-        <v>1552.4</v>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
+        <v>870.14</v>
+      </c>
+    </row>
+    <row r="41" ht="33" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>2646.28</v>
+        <v>3199.68</v>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F41" s="20">
@@ -2928,31 +2214,31 @@
         <v/>
       </c>
       <c r="I41" s="13" t="n">
-        <v>2222.88</v>
-      </c>
-    </row>
-    <row r="42" ht="14" customHeight="1">
+        <v>2687.73</v>
+      </c>
+    </row>
+    <row r="42" ht="44" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>30.170.4002</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>LED projektör, ışık akısı en az 5100 lm</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>9896.620000000001</v>
+        <v>835.1</v>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F42" s="20">
@@ -2968,526 +2254,6 @@
         <v/>
       </c>
       <c r="I42" s="13" t="n">
-        <v>8313.16</v>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>30.172.1706</t>
-        </is>
-      </c>
-      <c r="B43" s="18" t="inlineStr">
-        <is>
-          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>9265.620000000001</v>
-      </c>
-      <c r="E43" s="19" t="inlineStr">
-        <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
-        </is>
-      </c>
-      <c r="F43" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G43" s="5">
-        <f>D43*(1-F43)</f>
-        <v/>
-      </c>
-      <c r="H43" s="5">
-        <f>D43*$D$3</f>
-        <v/>
-      </c>
-      <c r="I43" s="13" t="n">
-        <v>7783.12</v>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>30.740.1106</t>
-        </is>
-      </c>
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>576288.2</v>
-      </c>
-      <c r="E44" s="19" t="inlineStr">
-        <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
-        </is>
-      </c>
-      <c r="F44" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G44" s="5">
-        <f>D44*(1-F44)</f>
-        <v/>
-      </c>
-      <c r="H44" s="5">
-        <f>D44*$D$3</f>
-        <v/>
-      </c>
-      <c r="I44" s="13" t="n">
-        <v>484082.09</v>
-      </c>
-    </row>
-    <row r="45" ht="14" customHeight="1">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>30.740.5406</t>
-        </is>
-      </c>
-      <c r="B45" s="18" t="inlineStr">
-        <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>99145.64999999999</v>
-      </c>
-      <c r="E45" s="19" t="inlineStr">
-        <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
-        </is>
-      </c>
-      <c r="F45" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G45" s="5">
-        <f>D45*(1-F45)</f>
-        <v/>
-      </c>
-      <c r="H45" s="5">
-        <f>D45*$D$3</f>
-        <v/>
-      </c>
-      <c r="I45" s="13" t="n">
-        <v>83282.35000000001</v>
-      </c>
-    </row>
-    <row r="46" ht="14" customHeight="1">
-      <c r="A46" s="17" t="inlineStr">
-        <is>
-          <t>30.750.1502</t>
-        </is>
-      </c>
-      <c r="B46" s="18" t="inlineStr">
-        <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>20726.2</v>
-      </c>
-      <c r="E46" s="19" t="inlineStr">
-        <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
-        </is>
-      </c>
-      <c r="F46" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G46" s="5">
-        <f>D46*(1-F46)</f>
-        <v/>
-      </c>
-      <c r="H46" s="5">
-        <f>D46*$D$3</f>
-        <v/>
-      </c>
-      <c r="I46" s="13" t="n">
-        <v>17410.01</v>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="17" t="inlineStr">
-        <is>
-          <t>30.750.2001</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="inlineStr">
-        <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>572.8</v>
-      </c>
-      <c r="E47" s="19" t="inlineStr">
-        <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
-        </is>
-      </c>
-      <c r="F47" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G47" s="5">
-        <f>D47*(1-F47)</f>
-        <v/>
-      </c>
-      <c r="H47" s="5">
-        <f>D47*$D$3</f>
-        <v/>
-      </c>
-      <c r="I47" s="13" t="n">
-        <v>481.15</v>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="17" t="inlineStr">
-        <is>
-          <t>30.750.3002</t>
-        </is>
-      </c>
-      <c r="B48" s="18" t="inlineStr">
-        <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>185.85</v>
-      </c>
-      <c r="E48" s="19" t="inlineStr">
-        <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
-        </is>
-      </c>
-      <c r="F48" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G48" s="5">
-        <f>D48*(1-F48)</f>
-        <v/>
-      </c>
-      <c r="H48" s="5">
-        <f>D48*$D$3</f>
-        <v/>
-      </c>
-      <c r="I48" s="13" t="n">
-        <v>156.11</v>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="17" t="inlineStr">
-        <is>
-          <t>43.527.1001</t>
-        </is>
-      </c>
-      <c r="B49" s="18" t="inlineStr">
-        <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>393.69</v>
-      </c>
-      <c r="E49" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F49" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G49" s="5">
-        <f>D49*(1-F49)</f>
-        <v/>
-      </c>
-      <c r="H49" s="5">
-        <f>D49*$D$3</f>
-        <v/>
-      </c>
-      <c r="I49" s="13" t="n">
-        <v>330.7</v>
-      </c>
-    </row>
-    <row r="50" ht="33" customHeight="1">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0042</t>
-        </is>
-      </c>
-      <c r="B50" s="18" t="inlineStr">
-        <is>
-          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>1624.67</v>
-      </c>
-      <c r="E50" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F50" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G50" s="5">
-        <f>D50*(1-F50)</f>
-        <v/>
-      </c>
-      <c r="H50" s="5">
-        <f>D50*$D$3</f>
-        <v/>
-      </c>
-      <c r="I50" s="13" t="n">
-        <v>1364.72</v>
-      </c>
-    </row>
-    <row r="51" ht="14" customHeight="1">
-      <c r="A51" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0091</t>
-        </is>
-      </c>
-      <c r="B51" s="18" t="inlineStr">
-        <is>
-          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>1120.05</v>
-      </c>
-      <c r="E51" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F51" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G51" s="5">
-        <f>D51*(1-F51)</f>
-        <v/>
-      </c>
-      <c r="H51" s="5">
-        <f>D51*$D$3</f>
-        <v/>
-      </c>
-      <c r="I51" s="13" t="n">
-        <v>940.84</v>
-      </c>
-    </row>
-    <row r="52" ht="14" customHeight="1">
-      <c r="A52" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0115</t>
-        </is>
-      </c>
-      <c r="B52" s="18" t="inlineStr">
-        <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>271.25</v>
-      </c>
-      <c r="E52" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F52" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G52" s="5">
-        <f>D52*(1-F52)</f>
-        <v/>
-      </c>
-      <c r="H52" s="5">
-        <f>D52*$D$3</f>
-        <v/>
-      </c>
-      <c r="I52" s="13" t="n">
-        <v>227.85</v>
-      </c>
-    </row>
-    <row r="53" ht="33" customHeight="1">
-      <c r="A53" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0151</t>
-        </is>
-      </c>
-      <c r="B53" s="18" t="inlineStr">
-        <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>1035.88</v>
-      </c>
-      <c r="E53" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F53" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G53" s="5">
-        <f>D53*(1-F53)</f>
-        <v/>
-      </c>
-      <c r="H53" s="5">
-        <f>D53*$D$3</f>
-        <v/>
-      </c>
-      <c r="I53" s="13" t="n">
-        <v>870.14</v>
-      </c>
-    </row>
-    <row r="54" ht="33" customHeight="1">
-      <c r="A54" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0175</t>
-        </is>
-      </c>
-      <c r="B54" s="18" t="inlineStr">
-        <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>3199.68</v>
-      </c>
-      <c r="E54" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F54" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G54" s="5">
-        <f>D54*(1-F54)</f>
-        <v/>
-      </c>
-      <c r="H54" s="5">
-        <f>D54*$D$3</f>
-        <v/>
-      </c>
-      <c r="I54" s="13" t="n">
-        <v>2687.73</v>
-      </c>
-    </row>
-    <row r="55" ht="44" customHeight="1">
-      <c r="A55" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0177</t>
-        </is>
-      </c>
-      <c r="B55" s="18" t="inlineStr">
-        <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>835.1</v>
-      </c>
-      <c r="E55" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F55" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G55" s="5">
-        <f>D55*(1-F55)</f>
-        <v/>
-      </c>
-      <c r="H55" s="5">
-        <f>D55*$D$3</f>
-        <v/>
-      </c>
-      <c r="I55" s="13" t="n">
         <v>701.48</v>
       </c>
     </row>
@@ -3506,7 +2272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3945,7 +2711,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
+    <row r="18" ht="14" customHeight="1">
       <c r="A18" s="21" t="inlineStr">
         <is>
           <t>Çatı ve sundurma işleri</t>
@@ -3953,21 +2719,21 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0042</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E18" s="23" t="n">
-        <v>1204.98</v>
+        <v>360.16</v>
       </c>
       <c r="F18" s="24">
         <f>IFERROR(VLOOKUP($B18,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3978,25 +2744,29 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="14" customHeight="1">
-      <c r="A19" s="26" t="n"/>
+    <row r="19" ht="33" customHeight="1">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+        </is>
+      </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>360.16</v>
+        <v>13.4</v>
       </c>
       <c r="F19" s="24">
         <f>IFERROR(VLOOKUP($B19,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4007,20 +2777,16 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="33" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
-        </is>
-      </c>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="25" t="n"/>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -4029,7 +2795,7 @@
         </is>
       </c>
       <c r="E20" s="23" t="n">
-        <v>13.4</v>
+        <v>5.67</v>
       </c>
       <c r="F20" s="24">
         <f>IFERROR(VLOOKUP($B20,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4041,24 +2807,24 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="25" t="n"/>
+      <c r="A21" s="26" t="n"/>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>5.67</v>
+        <v>54.315</v>
       </c>
       <c r="F21" s="24">
         <f>IFERROR(VLOOKUP($B21,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4069,25 +2835,29 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="26" t="n"/>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Sıva, alçı, derz ve şap işleri</t>
+        </is>
+      </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E22" s="23" t="n">
-        <v>54.315</v>
+        <v>557.76</v>
       </c>
       <c r="F22" s="24">
         <f>IFERROR(VLOOKUP($B22,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4098,20 +2868,16 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
-        </is>
-      </c>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="26" t="n"/>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -4120,7 +2886,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>557.76</v>
+        <v>647.76</v>
       </c>
       <c r="F23" s="24">
         <f>IFERROR(VLOOKUP($B23,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4132,15 +2898,19 @@
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="26" t="n"/>
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Boya, badana ve cila işleri</t>
+        </is>
+      </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -4149,7 +2919,7 @@
         </is>
       </c>
       <c r="E24" s="23" t="n">
-        <v>647.76</v>
+        <v>557.76</v>
       </c>
       <c r="F24" s="24">
         <f>IFERROR(VLOOKUP($B24,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4161,19 +2931,15 @@
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>Boya, badana ve cila işleri</t>
-        </is>
-      </c>
+      <c r="A25" s="26" t="n"/>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -4182,7 +2948,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>557.76</v>
+        <v>612.76</v>
       </c>
       <c r="F25" s="24">
         <f>IFERROR(VLOOKUP($B25,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4193,16 +2959,20 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="26" t="n"/>
+    <row r="26" ht="33" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+        </is>
+      </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -4211,7 +2981,7 @@
         </is>
       </c>
       <c r="E26" s="23" t="n">
-        <v>612.76</v>
+        <v>60</v>
       </c>
       <c r="F26" s="24">
         <f>IFERROR(VLOOKUP($B26,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4222,29 +2992,29 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="33" customHeight="1">
+    <row r="27" ht="22" customHeight="1">
       <c r="A27" s="21" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F27" s="24">
         <f>IFERROR(VLOOKUP($B27,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4255,29 +3025,29 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="22" customHeight="1">
+    <row r="28" ht="14" customHeight="1">
       <c r="A28" s="21" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>30.100.2105</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E28" s="23" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F28" s="24">
         <f>IFERROR(VLOOKUP($B28,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4289,19 +3059,15 @@
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
-      <c r="A29" s="21" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
+      <c r="A29" s="25" t="n"/>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -4325,12 +3091,12 @@
       <c r="A30" s="25" t="n"/>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4339,7 +3105,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="24">
         <f>IFERROR(VLOOKUP($B30,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4354,21 +3120,21 @@
       <c r="A31" s="25" t="n"/>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="F31" s="24">
         <f>IFERROR(VLOOKUP($B31,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4379,25 +3145,25 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="14" customHeight="1">
+    <row r="32" ht="22" customHeight="1">
       <c r="A32" s="25" t="n"/>
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="F32" s="24">
         <f>IFERROR(VLOOKUP($B32,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4412,12 +3178,12 @@
       <c r="A33" s="25" t="n"/>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4426,7 +3192,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F33" s="24">
         <f>IFERROR(VLOOKUP($B33,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4437,25 +3203,25 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
+    <row r="34" ht="14" customHeight="1">
       <c r="A34" s="25" t="n"/>
       <c r="B34" s="22" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="F34" s="24">
         <f>IFERROR(VLOOKUP($B34,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4470,12 +3236,12 @@
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -4484,7 +3250,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="F35" s="24">
         <f>IFERROR(VLOOKUP($B35,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4499,12 +3265,12 @@
       <c r="A36" s="25" t="n"/>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -4513,7 +3279,7 @@
         </is>
       </c>
       <c r="E36" s="23" t="n">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="F36" s="24">
         <f>IFERROR(VLOOKUP($B36,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4528,12 +3294,12 @@
       <c r="A37" s="25" t="n"/>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -4542,7 +3308,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F37" s="24">
         <f>IFERROR(VLOOKUP($B37,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4553,16 +3319,16 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="14" customHeight="1">
+    <row r="38" ht="22" customHeight="1">
       <c r="A38" s="25" t="n"/>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -4571,7 +3337,7 @@
         </is>
       </c>
       <c r="E38" s="23" t="n">
-        <v>100</v>
+        <v>186</v>
       </c>
       <c r="F38" s="24">
         <f>IFERROR(VLOOKUP($B38,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4582,25 +3348,25 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="22" customHeight="1">
+    <row r="39" ht="14" customHeight="1">
       <c r="A39" s="25" t="n"/>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F39" s="24">
         <f>IFERROR(VLOOKUP($B39,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4611,25 +3377,25 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="14" customHeight="1">
+    <row r="40" ht="22" customHeight="1">
       <c r="A40" s="25" t="n"/>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E40" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F40" s="24">
         <f>IFERROR(VLOOKUP($B40,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4644,21 +3410,21 @@
       <c r="A41" s="25" t="n"/>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F41" s="24">
         <f>IFERROR(VLOOKUP($B41,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4669,16 +3435,16 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="25" t="n"/>
+    <row r="42" ht="14" customHeight="1">
+      <c r="A42" s="26" t="n"/>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>30.740.5406</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -4698,92 +3464,33 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="25" t="n"/>
-      <c r="B43" s="22" t="inlineStr">
-        <is>
-          <t>30.740.5406</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="24">
-        <f>IFERROR(VLOOKUP($B43,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G43" s="5">
-        <f>E43*F43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="26" t="n"/>
-      <c r="B44" s="22" t="inlineStr">
-        <is>
-          <t>30.120.2016</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>Otomatik transfer şalteri 4 x 200 A</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E44" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="24">
-        <f>IFERROR(VLOOKUP($B44,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G44" s="5">
-        <f>E44*F44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="n"/>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="27" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="11" t="n"/>
-      <c r="G45" s="13">
-        <f>SUM(G6:G44)</f>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="13">
+        <f>SUM(G6:G42)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A22:A23"/>
     <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A42"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A29:A44"/>
-    <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4795,7 +3502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5234,7 +3941,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
+    <row r="18" ht="14" customHeight="1">
       <c r="A18" s="21" t="inlineStr">
         <is>
           <t>Çatı ve sundurma işleri</t>
@@ -5242,21 +3949,21 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0042</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E18" s="23" t="n">
-        <v>1204.98</v>
+        <v>360.16</v>
       </c>
       <c r="F18" s="24">
         <f>IFERROR(VLOOKUP($B18,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5267,25 +3974,29 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="14" customHeight="1">
-      <c r="A19" s="26" t="n"/>
+    <row r="19" ht="33" customHeight="1">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+        </is>
+      </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>360.16</v>
+        <v>13.4</v>
       </c>
       <c r="F19" s="24">
         <f>IFERROR(VLOOKUP($B19,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5296,20 +4007,16 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="33" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
-        </is>
-      </c>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="25" t="n"/>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -5318,7 +4025,7 @@
         </is>
       </c>
       <c r="E20" s="23" t="n">
-        <v>13.4</v>
+        <v>5.67</v>
       </c>
       <c r="F20" s="24">
         <f>IFERROR(VLOOKUP($B20,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5330,24 +4037,24 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="25" t="n"/>
+      <c r="A21" s="26" t="n"/>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>5.67</v>
+        <v>54.315</v>
       </c>
       <c r="F21" s="24">
         <f>IFERROR(VLOOKUP($B21,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5358,25 +4065,29 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="26" t="n"/>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Sıva, alçı, derz ve şap işleri</t>
+        </is>
+      </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E22" s="23" t="n">
-        <v>54.315</v>
+        <v>557.76</v>
       </c>
       <c r="F22" s="24">
         <f>IFERROR(VLOOKUP($B22,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5387,20 +4098,16 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
-        </is>
-      </c>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="26" t="n"/>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -5409,7 +4116,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>557.76</v>
+        <v>647.76</v>
       </c>
       <c r="F23" s="24">
         <f>IFERROR(VLOOKUP($B23,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5421,15 +4128,19 @@
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="26" t="n"/>
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Boya, badana ve cila işleri</t>
+        </is>
+      </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -5438,7 +4149,7 @@
         </is>
       </c>
       <c r="E24" s="23" t="n">
-        <v>647.76</v>
+        <v>557.76</v>
       </c>
       <c r="F24" s="24">
         <f>IFERROR(VLOOKUP($B24,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5450,19 +4161,15 @@
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>Boya, badana ve cila işleri</t>
-        </is>
-      </c>
+      <c r="A25" s="26" t="n"/>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -5471,7 +4178,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>557.76</v>
+        <v>612.76</v>
       </c>
       <c r="F25" s="24">
         <f>IFERROR(VLOOKUP($B25,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5482,16 +4189,20 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="26" t="n"/>
+    <row r="26" ht="33" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+        </is>
+      </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -5500,7 +4211,7 @@
         </is>
       </c>
       <c r="E26" s="23" t="n">
-        <v>612.76</v>
+        <v>60</v>
       </c>
       <c r="F26" s="24">
         <f>IFERROR(VLOOKUP($B26,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5511,29 +4222,29 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="33" customHeight="1">
+    <row r="27" ht="22" customHeight="1">
       <c r="A27" s="21" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F27" s="24">
         <f>IFERROR(VLOOKUP($B27,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5544,29 +4255,29 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="22" customHeight="1">
+    <row r="28" ht="14" customHeight="1">
       <c r="A28" s="21" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>30.100.2105</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E28" s="23" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F28" s="24">
         <f>IFERROR(VLOOKUP($B28,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5578,19 +4289,15 @@
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
-      <c r="A29" s="21" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
+      <c r="A29" s="25" t="n"/>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -5614,12 +4321,12 @@
       <c r="A30" s="25" t="n"/>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -5628,7 +4335,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="24">
         <f>IFERROR(VLOOKUP($B30,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5643,21 +4350,21 @@
       <c r="A31" s="25" t="n"/>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="F31" s="24">
         <f>IFERROR(VLOOKUP($B31,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5668,25 +4375,25 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="14" customHeight="1">
+    <row r="32" ht="22" customHeight="1">
       <c r="A32" s="25" t="n"/>
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="F32" s="24">
         <f>IFERROR(VLOOKUP($B32,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5701,12 +4408,12 @@
       <c r="A33" s="25" t="n"/>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -5715,7 +4422,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F33" s="24">
         <f>IFERROR(VLOOKUP($B33,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5726,25 +4433,25 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
+    <row r="34" ht="14" customHeight="1">
       <c r="A34" s="25" t="n"/>
       <c r="B34" s="22" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="F34" s="24">
         <f>IFERROR(VLOOKUP($B34,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5759,12 +4466,12 @@
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -5773,7 +4480,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="F35" s="24">
         <f>IFERROR(VLOOKUP($B35,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5788,12 +4495,12 @@
       <c r="A36" s="25" t="n"/>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -5802,7 +4509,7 @@
         </is>
       </c>
       <c r="E36" s="23" t="n">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="F36" s="24">
         <f>IFERROR(VLOOKUP($B36,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5817,12 +4524,12 @@
       <c r="A37" s="25" t="n"/>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5831,7 +4538,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F37" s="24">
         <f>IFERROR(VLOOKUP($B37,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5842,16 +4549,16 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="14" customHeight="1">
+    <row r="38" ht="22" customHeight="1">
       <c r="A38" s="25" t="n"/>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -5860,7 +4567,7 @@
         </is>
       </c>
       <c r="E38" s="23" t="n">
-        <v>100</v>
+        <v>186</v>
       </c>
       <c r="F38" s="24">
         <f>IFERROR(VLOOKUP($B38,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5871,25 +4578,25 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="22" customHeight="1">
+    <row r="39" ht="14" customHeight="1">
       <c r="A39" s="25" t="n"/>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F39" s="24">
         <f>IFERROR(VLOOKUP($B39,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5900,25 +4607,25 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="14" customHeight="1">
+    <row r="40" ht="22" customHeight="1">
       <c r="A40" s="25" t="n"/>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E40" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F40" s="24">
         <f>IFERROR(VLOOKUP($B40,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5933,21 +4640,21 @@
       <c r="A41" s="25" t="n"/>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F41" s="24">
         <f>IFERROR(VLOOKUP($B41,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5958,16 +4665,16 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="25" t="n"/>
+    <row r="42" ht="14" customHeight="1">
+      <c r="A42" s="26" t="n"/>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>30.740.5406</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -5987,1417 +4694,33 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="25" t="n"/>
-      <c r="B43" s="22" t="inlineStr">
-        <is>
-          <t>30.740.5406</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="24">
-        <f>IFERROR(VLOOKUP($B43,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G43" s="5">
-        <f>E43*F43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="26" t="n"/>
-      <c r="B44" s="22" t="inlineStr">
-        <is>
-          <t>30.120.2016</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>Otomatik transfer şalteri 4 x 200 A</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E44" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="24">
-        <f>IFERROR(VLOOKUP($B44,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G44" s="5">
-        <f>E44*F44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="n"/>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="27" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="11" t="n"/>
-      <c r="G45" s="13">
-        <f>SUM(G6:G44)</f>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="13">
+        <f>SUM(G6:G42)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A22:A23"/>
     <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A42"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A29:A44"/>
-    <mergeCell ref="A18:A19"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KEŞİF ÖZETİ — GÜBRE ÇUKURU</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Musab Eder Çiftliği — Kocaeli / Karamürsel / İnebeyli Mah., 138 ada 17 parsel · inşaat alanı 115,00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>EK-1 uygun harcama kalemi</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Yapım işinin adı</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Miktar</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Birim fiyat (TL)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Tutar (TL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="n">
-        <v>542.7</v>
-      </c>
-      <c r="F6" s="24">
-        <f>IFERROR(VLOOKUP($B6,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="5">
-        <f>E6*F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="n">
-        <v>11.934</v>
-      </c>
-      <c r="F7" s="24">
-        <f>IFERROR(VLOOKUP($B7,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="5">
-        <f>E7*F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>93.19</v>
-      </c>
-      <c r="F8" s="24">
-        <f>IFERROR(VLOOKUP($B8,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="5">
-        <f>E8*F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="n">
-        <v>363.26</v>
-      </c>
-      <c r="F9" s="24">
-        <f>IFERROR(VLOOKUP($B9,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="5">
-        <f>E9*F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="n">
-        <v>7.5993</v>
-      </c>
-      <c r="F10" s="24">
-        <f>IFERROR(VLOOKUP($B10,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="5">
-        <f>E10*F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="26" t="n"/>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>15.160.1004</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="n">
-        <v>0.5641</v>
-      </c>
-      <c r="F11" s="24">
-        <f>IFERROR(VLOOKUP($B11,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="5">
-        <f>E11*F11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="27" t="inlineStr">
-        <is>
-          <t>TOPLAM (KDV hariç)</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="13">
-        <f>SUM(G6:G11)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KEŞİF ÖZETİ — ÖLÜ ATMA ÇUKURU</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Musab Eder Çiftliği — Kocaeli / Karamürsel / İnebeyli Mah., 138 ada 17 parsel · inşaat alanı 18,00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>EK-1 uygun harcama kalemi</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Yapım işinin adı</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Miktar</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Birim fiyat (TL)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Tutar (TL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="n">
-        <v>142</v>
-      </c>
-      <c r="F6" s="24">
-        <f>IFERROR(VLOOKUP($B6,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="5">
-        <f>E6*F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="n">
-        <v>1.984</v>
-      </c>
-      <c r="F7" s="24">
-        <f>IFERROR(VLOOKUP($B7,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="5">
-        <f>E7*F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="F8" s="24">
-        <f>IFERROR(VLOOKUP($B8,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="5">
-        <f>E8*F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="n">
-        <v>127.2</v>
-      </c>
-      <c r="F9" s="24">
-        <f>IFERROR(VLOOKUP($B9,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="5">
-        <f>E9*F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="n">
-        <v>1.6571</v>
-      </c>
-      <c r="F10" s="24">
-        <f>IFERROR(VLOOKUP($B10,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="5">
-        <f>E10*F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="27" t="inlineStr">
-        <is>
-          <t>TOPLAM (KDV hariç)</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="13">
-        <f>SUM(G6:G10)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KEŞİF ÖZETİ — FOSEPTIK</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Musab Eder Çiftliği — Kocaeli / Karamürsel / İnebeyli Mah., 138 ada 17 parsel · inşaat alanı 4,00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>EK-1 uygun harcama kalemi</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Yapım işinin adı</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Miktar</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Birim fiyat (TL)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Tutar (TL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="F6" s="24">
-        <f>IFERROR(VLOOKUP($B6,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="5">
-        <f>E6*F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="n">
-        <v>0.484</v>
-      </c>
-      <c r="F7" s="24">
-        <f>IFERROR(VLOOKUP($B7,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="5">
-        <f>E7*F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>6.175</v>
-      </c>
-      <c r="F8" s="24">
-        <f>IFERROR(VLOOKUP($B8,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="5">
-        <f>E8*F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="F9" s="24">
-        <f>IFERROR(VLOOKUP($B9,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="5">
-        <f>E9*F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="n">
-        <v>0.5866</v>
-      </c>
-      <c r="F10" s="24">
-        <f>IFERROR(VLOOKUP($B10,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="5">
-        <f>E10*F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="27" t="inlineStr">
-        <is>
-          <t>TOPLAM (KDV hariç)</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="13">
-        <f>SUM(G6:G10)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KEŞİF ÖZETİ — YEM SILOSU BETONARME KAIDELERI</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Musab Eder Çiftliği — Kocaeli / Karamürsel / İnebeyli Mah., 138 ada 17 parsel · inşaat alanı 16,82 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>EK-1 uygun harcama kalemi</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Yapım işinin adı</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Miktar</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Birim fiyat (TL)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Tutar (TL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="F6" s="24">
-        <f>IFERROR(VLOOKUP($B6,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="5">
-        <f>E6*F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="n">
-        <v>1.922</v>
-      </c>
-      <c r="F7" s="24">
-        <f>IFERROR(VLOOKUP($B7,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="5">
-        <f>E7*F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>8.41</v>
-      </c>
-      <c r="F8" s="24">
-        <f>IFERROR(VLOOKUP($B8,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="5">
-        <f>E8*F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F9" s="24">
-        <f>IFERROR(VLOOKUP($B9,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="5">
-        <f>E9*F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="n">
-        <v>0.7569</v>
-      </c>
-      <c r="F10" s="24">
-        <f>IFERROR(VLOOKUP($B10,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="5">
-        <f>E10*F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="27" t="inlineStr">
-        <is>
-          <t>TOPLAM (KDV hariç)</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="13">
-        <f>SUM(G6:G10)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KEŞİF ÖZETİ — SU DEPOSU</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Musab Eder Çiftliği — Kocaeli / Karamürsel / İnebeyli Mah., 138 ada 17 parsel · inşaat alanı 12,00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>EK-1 uygun harcama kalemi</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Yapım işinin adı</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Miktar</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Birim fiyat (TL)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Tutar (TL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="n">
-        <v>106.5</v>
-      </c>
-      <c r="F6" s="24">
-        <f>IFERROR(VLOOKUP($B6,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="5">
-        <f>E6*F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="n">
-        <v>1.344</v>
-      </c>
-      <c r="F7" s="24">
-        <f>IFERROR(VLOOKUP($B7,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="5">
-        <f>E7*F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>15.15</v>
-      </c>
-      <c r="F8" s="24">
-        <f>IFERROR(VLOOKUP($B8,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="5">
-        <f>E8*F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="F9" s="24">
-        <f>IFERROR(VLOOKUP($B9,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="5">
-        <f>E9*F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="n">
-        <v>1.2316</v>
-      </c>
-      <c r="F10" s="24">
-        <f>IFERROR(VLOOKUP($B10,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="5">
-        <f>E10*F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="27" t="inlineStr">
-        <is>
-          <t>TOPLAM (KDV hariç)</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="13">
-        <f>SUM(G6:G10)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -1465,7 +1465,7 @@
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>12003.52</v>
+        <v>8433.52</v>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F23" s="20">
@@ -1494,7 +1494,7 @@
         <v/>
       </c>
       <c r="I23" s="13" t="n">
-        <v>10082.96</v>
+        <v>7084.16</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1514,11 +1514,11 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>5280.06</v>
+        <v>4200.06</v>
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F24" s="20">
@@ -1534,10 +1534,10 @@
         <v/>
       </c>
       <c r="I24" s="13" t="n">
-        <v>4435.25</v>
-      </c>
-    </row>
-    <row r="25" ht="14" customHeight="1">
+        <v>3528.05</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
         <is>
           <t>30.115.1003</t>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1554,11 +1554,11 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1709.76</v>
+        <v>1284.76</v>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F25" s="20">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="I25" s="13" t="n">
-        <v>1436.2</v>
+        <v>1079.2</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1594,11 +1594,11 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>223.96</v>
+        <v>186.96</v>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F26" s="20">
@@ -1614,7 +1614,7 @@
         <v/>
       </c>
       <c r="I26" s="13" t="n">
-        <v>188.13</v>
+        <v>157.05</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1634,11 +1634,11 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>290.5</v>
+        <v>238.1</v>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F27" s="20">
@@ -1654,10 +1654,10 @@
         <v/>
       </c>
       <c r="I27" s="13" t="n">
-        <v>244.02</v>
-      </c>
-    </row>
-    <row r="28" ht="14" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
           <t>30.150.1401</t>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>28.05</v>
+        <v>14.55</v>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F28" s="20">
@@ -1694,10 +1694,10 @@
         <v/>
       </c>
       <c r="I28" s="13" t="n">
-        <v>23.56</v>
-      </c>
-    </row>
-    <row r="29" ht="14" customHeight="1">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
         <is>
           <t>30.150.1402</t>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1714,11 +1714,11 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>39.41</v>
+        <v>23.21</v>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F29" s="20">
@@ -1734,10 +1734,10 @@
         <v/>
       </c>
       <c r="I29" s="13" t="n">
-        <v>33.1</v>
-      </c>
-    </row>
-    <row r="30" ht="14" customHeight="1">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
           <t>30.160.6102</t>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1754,11 +1754,11 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>88.59</v>
+        <v>34.59</v>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F30" s="20">
@@ -1774,7 +1774,7 @@
         <v/>
       </c>
       <c r="I30" s="13" t="n">
-        <v>74.42</v>
+        <v>29.06</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -1794,11 +1794,11 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1848.1</v>
+        <v>1632.1</v>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F31" s="20">
@@ -1814,10 +1814,10 @@
         <v/>
       </c>
       <c r="I31" s="13" t="n">
-        <v>1552.4</v>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
+        <v>1370.96</v>
+      </c>
+    </row>
+    <row r="32" ht="33" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
           <t>30.170.1602</t>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1834,11 +1834,11 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>2646.28</v>
+        <v>2376.28</v>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F32" s="20">
@@ -1854,10 +1854,10 @@
         <v/>
       </c>
       <c r="I32" s="13" t="n">
-        <v>2222.88</v>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
+        <v>1996.08</v>
+      </c>
+    </row>
+    <row r="33" ht="33" customHeight="1">
       <c r="A33" s="17" t="inlineStr">
         <is>
           <t>30.740.1106</t>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1874,11 +1874,11 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>576288.2</v>
+        <v>556368.2</v>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F33" s="20">
@@ -1894,10 +1894,10 @@
         <v/>
       </c>
       <c r="I33" s="13" t="n">
-        <v>484082.09</v>
-      </c>
-    </row>
-    <row r="34" ht="14" customHeight="1">
+        <v>467349.29</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
           <t>30.740.5406</t>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1914,11 +1914,11 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>99145.64999999999</v>
+        <v>94825.64999999999</v>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F34" s="20">
@@ -1934,10 +1934,10 @@
         <v/>
       </c>
       <c r="I34" s="13" t="n">
-        <v>83282.35000000001</v>
-      </c>
-    </row>
-    <row r="35" ht="14" customHeight="1">
+        <v>79653.55</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
       <c r="A35" s="17" t="inlineStr">
         <is>
           <t>30.750.1502</t>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -1954,11 +1954,11 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>20726.2</v>
+        <v>18566.2</v>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F35" s="20">
@@ -1974,7 +1974,7 @@
         <v/>
       </c>
       <c r="I35" s="13" t="n">
-        <v>17410.01</v>
+        <v>15595.61</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -1994,11 +1994,11 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>572.8</v>
+        <v>508</v>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F36" s="20">
@@ -2014,7 +2014,7 @@
         <v/>
       </c>
       <c r="I36" s="13" t="n">
-        <v>481.15</v>
+        <v>426.72</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2034,11 +2034,11 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>185.85</v>
+        <v>138.05</v>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25 + montaj</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F37" s="20">
@@ -2054,7 +2054,7 @@
         <v/>
       </c>
       <c r="I37" s="13" t="n">
-        <v>156.11</v>
+        <v>115.96</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
@@ -3025,7 +3025,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="14" customHeight="1">
+    <row r="28" ht="22" customHeight="1">
       <c r="A28" s="21" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -3058,7 +3058,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="14" customHeight="1">
+    <row r="29" ht="22" customHeight="1">
       <c r="A29" s="25" t="n"/>
       <c r="B29" s="22" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -3116,7 +3116,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="14" customHeight="1">
+    <row r="31" ht="22" customHeight="1">
       <c r="A31" s="25" t="n"/>
       <c r="B31" s="22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -3232,7 +3232,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="14" customHeight="1">
+    <row r="35" ht="22" customHeight="1">
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="22" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -3261,7 +3261,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="14" customHeight="1">
+    <row r="36" ht="22" customHeight="1">
       <c r="A36" s="25" t="n"/>
       <c r="B36" s="22" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -3290,7 +3290,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="14" customHeight="1">
+    <row r="37" ht="22" customHeight="1">
       <c r="A37" s="25" t="n"/>
       <c r="B37" s="22" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -3348,7 +3348,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="14" customHeight="1">
+    <row r="39" ht="22" customHeight="1">
       <c r="A39" s="25" t="n"/>
       <c r="B39" s="22" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -4255,7 +4255,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="14" customHeight="1">
+    <row r="28" ht="22" customHeight="1">
       <c r="A28" s="21" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -4288,7 +4288,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="14" customHeight="1">
+    <row r="29" ht="22" customHeight="1">
       <c r="A29" s="25" t="n"/>
       <c r="B29" s="22" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4346,7 +4346,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="14" customHeight="1">
+    <row r="31" ht="22" customHeight="1">
       <c r="A31" s="25" t="n"/>
       <c r="B31" s="22" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -4462,7 +4462,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="14" customHeight="1">
+    <row r="35" ht="22" customHeight="1">
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="22" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -4491,7 +4491,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="14" customHeight="1">
+    <row r="36" ht="22" customHeight="1">
       <c r="A36" s="25" t="n"/>
       <c r="B36" s="22" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -4520,7 +4520,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="14" customHeight="1">
+    <row r="37" ht="22" customHeight="1">
       <c r="A37" s="25" t="n"/>
       <c r="B37" s="22" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -4578,7 +4578,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="14" customHeight="1">
+    <row r="39" ht="22" customHeight="1">
       <c r="A39" s="25" t="n"/>
       <c r="B39" s="22" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="C4" s="5">
-        <f>'01 Kümes A Blok'!$G$43</f>
+        <f>'01 Kümes A Blok'!$G$44</f>
         <v/>
       </c>
       <c r="D4" s="6">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>'02 Kümes B Blok'!$G$43</f>
+        <f>'02 Kümes B Blok'!$G$44</f>
         <v/>
       </c>
       <c r="D5" s="6">
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1300,21 +1300,21 @@
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
+          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>296.13</v>
+        <v>207.41</v>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
@@ -1334,18 +1334,18 @@
         <v/>
       </c>
       <c r="I19" s="13" t="n">
-        <v>248.75</v>
+        <v>174.22</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>386.03</v>
+        <v>296.13</v>
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
@@ -1374,27 +1374,27 @@
         <v/>
       </c>
       <c r="I20" s="13" t="n">
-        <v>324.27</v>
+        <v>248.75</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>218.54</v>
+        <v>386.03</v>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
@@ -1414,18 +1414,18 @@
         <v/>
       </c>
       <c r="I21" s="13" t="n">
-        <v>183.57</v>
+        <v>324.27</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>175.8</v>
+        <v>218.54</v>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
@@ -1454,31 +1454,31 @@
         <v/>
       </c>
       <c r="I22" s="13" t="n">
-        <v>147.67</v>
+        <v>183.57</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
+          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>8433.52</v>
+        <v>175.8</v>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
+          <t>ÇŞB 2026 birim fiyat kitabı</t>
         </is>
       </c>
       <c r="F23" s="20">
@@ -1494,18 +1494,18 @@
         <v/>
       </c>
       <c r="I23" s="13" t="n">
-        <v>7084.16</v>
+        <v>147.67</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>30.100.2105</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>4200.06</v>
+        <v>8433.52</v>
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
@@ -1534,18 +1534,18 @@
         <v/>
       </c>
       <c r="I24" s="13" t="n">
-        <v>3528.05</v>
+        <v>7084.16</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1284.76</v>
+        <v>4200.06</v>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
@@ -1574,27 +1574,27 @@
         <v/>
       </c>
       <c r="I25" s="13" t="n">
-        <v>1079.2</v>
+        <v>3528.05</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>186.96</v>
+        <v>1284.76</v>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
@@ -1614,18 +1614,18 @@
         <v/>
       </c>
       <c r="I26" s="13" t="n">
-        <v>157.05</v>
+        <v>1079.2</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>238.1</v>
+        <v>186.96</v>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
@@ -1654,18 +1654,18 @@
         <v/>
       </c>
       <c r="I27" s="13" t="n">
-        <v>200</v>
+        <v>157.05</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>14.55</v>
+        <v>238.1</v>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
@@ -1694,18 +1694,18 @@
         <v/>
       </c>
       <c r="I28" s="13" t="n">
-        <v>12.22</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>23.21</v>
+        <v>14.55</v>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
@@ -1734,18 +1734,18 @@
         <v/>
       </c>
       <c r="I29" s="13" t="n">
-        <v>19.5</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>34.59</v>
+        <v>23.21</v>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
@@ -1774,27 +1774,27 @@
         <v/>
       </c>
       <c r="I30" s="13" t="n">
-        <v>29.06</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1632.1</v>
+        <v>34.59</v>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
@@ -1814,18 +1814,18 @@
         <v/>
       </c>
       <c r="I31" s="13" t="n">
-        <v>1370.96</v>
-      </c>
-    </row>
-    <row r="32" ht="33" customHeight="1">
+        <v>29.06</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>2376.28</v>
+        <v>1632.1</v>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
@@ -1854,18 +1854,18 @@
         <v/>
       </c>
       <c r="I32" s="13" t="n">
-        <v>1996.08</v>
+        <v>1370.96</v>
       </c>
     </row>
     <row r="33" ht="33" customHeight="1">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>556368.2</v>
+        <v>2376.28</v>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
@@ -1894,18 +1894,18 @@
         <v/>
       </c>
       <c r="I33" s="13" t="n">
-        <v>467349.29</v>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
+        <v>1996.08</v>
+      </c>
+    </row>
+    <row r="34" ht="33" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>94825.64999999999</v>
+        <v>556368.2</v>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
@@ -1934,18 +1934,18 @@
         <v/>
       </c>
       <c r="I34" s="13" t="n">
-        <v>79653.55</v>
+        <v>467349.29</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.740.5406</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>18566.2</v>
+        <v>94825.64999999999</v>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
@@ -1974,27 +1974,27 @@
         <v/>
       </c>
       <c r="I35" s="13" t="n">
-        <v>15595.61</v>
+        <v>79653.55</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>508</v>
+        <v>18566.2</v>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
@@ -2014,18 +2014,18 @@
         <v/>
       </c>
       <c r="I36" s="13" t="n">
-        <v>426.72</v>
+        <v>15595.61</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>138.05</v>
+        <v>508</v>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
@@ -2054,18 +2054,18 @@
         <v/>
       </c>
       <c r="I37" s="13" t="n">
-        <v>115.96</v>
+        <v>426.72</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2074,11 +2074,11 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>393.69</v>
+        <v>138.05</v>
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F38" s="20">
@@ -2094,27 +2094,27 @@
         <v/>
       </c>
       <c r="I38" s="13" t="n">
-        <v>330.7</v>
-      </c>
-    </row>
-    <row r="39" ht="14" customHeight="1">
+        <v>115.96</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>271.25</v>
+        <v>393.69</v>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
@@ -2134,27 +2134,27 @@
         <v/>
       </c>
       <c r="I39" s="13" t="n">
-        <v>227.85</v>
-      </c>
-    </row>
-    <row r="40" ht="33" customHeight="1">
+        <v>330.7</v>
+      </c>
+    </row>
+    <row r="40" ht="14" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1035.88</v>
+        <v>271.25</v>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
@@ -2174,18 +2174,18 @@
         <v/>
       </c>
       <c r="I40" s="13" t="n">
-        <v>870.14</v>
+        <v>227.85</v>
       </c>
     </row>
     <row r="41" ht="33" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>3199.68</v>
+        <v>1035.88</v>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
@@ -2214,18 +2214,18 @@
         <v/>
       </c>
       <c r="I41" s="13" t="n">
-        <v>2687.73</v>
-      </c>
-    </row>
-    <row r="42" ht="44" customHeight="1">
+        <v>870.14</v>
+      </c>
+    </row>
+    <row r="42" ht="33" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>835.1</v>
+        <v>3199.68</v>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
@@ -2254,6 +2254,46 @@
         <v/>
       </c>
       <c r="I42" s="13" t="n">
+        <v>2687.73</v>
+      </c>
+    </row>
+    <row r="43" ht="44" customHeight="1">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>TKDK-0177</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>835.1</v>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F43" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G43" s="5">
+        <f>D43*(1-F43)</f>
+        <v/>
+      </c>
+      <c r="H43" s="5">
+        <f>D43*$D$3</f>
+        <v/>
+      </c>
+      <c r="I43" s="13" t="n">
         <v>701.48</v>
       </c>
     </row>
@@ -2272,7 +2312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2733,7 +2773,7 @@
         </is>
       </c>
       <c r="E18" s="23" t="n">
-        <v>360.16</v>
+        <v>319.2</v>
       </c>
       <c r="F18" s="24">
         <f>IFERROR(VLOOKUP($B18,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -2744,29 +2784,25 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="33" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
-        </is>
-      </c>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="26" t="n"/>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>13.4</v>
+        <v>51.2</v>
       </c>
       <c r="F19" s="24">
         <f>IFERROR(VLOOKUP($B19,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -2777,16 +2813,20 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="25" t="n"/>
+    <row r="20" ht="33" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+        </is>
+      </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2795,7 +2835,7 @@
         </is>
       </c>
       <c r="E20" s="23" t="n">
-        <v>5.67</v>
+        <v>13.4</v>
       </c>
       <c r="F20" s="24">
         <f>IFERROR(VLOOKUP($B20,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -2807,24 +2847,24 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="26" t="n"/>
+      <c r="A21" s="25" t="n"/>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>54.315</v>
+        <v>5.67</v>
       </c>
       <c r="F21" s="24">
         <f>IFERROR(VLOOKUP($B21,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -2835,29 +2875,25 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="21" t="inlineStr">
-        <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
-        </is>
-      </c>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="26" t="n"/>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E22" s="23" t="n">
-        <v>557.76</v>
+        <v>54.315</v>
       </c>
       <c r="F22" s="24">
         <f>IFERROR(VLOOKUP($B22,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -2868,16 +2904,20 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="26" t="n"/>
+    <row r="23" ht="14" customHeight="1">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Sıva, alçı, derz ve şap işleri</t>
+        </is>
+      </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -2886,7 +2926,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>647.76</v>
+        <v>557.76</v>
       </c>
       <c r="F23" s="24">
         <f>IFERROR(VLOOKUP($B23,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -2898,19 +2938,15 @@
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>Boya, badana ve cila işleri</t>
-        </is>
-      </c>
+      <c r="A24" s="26" t="n"/>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2919,7 +2955,7 @@
         </is>
       </c>
       <c r="E24" s="23" t="n">
-        <v>557.76</v>
+        <v>647.76</v>
       </c>
       <c r="F24" s="24">
         <f>IFERROR(VLOOKUP($B24,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -2931,15 +2967,19 @@
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="26" t="n"/>
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Boya, badana ve cila işleri</t>
+        </is>
+      </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -2948,7 +2988,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>612.76</v>
+        <v>557.76</v>
       </c>
       <c r="F25" s="24">
         <f>IFERROR(VLOOKUP($B25,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -2959,20 +2999,16 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="33" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
-        </is>
-      </c>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="26" t="n"/>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -2981,7 +3017,7 @@
         </is>
       </c>
       <c r="E26" s="23" t="n">
-        <v>60</v>
+        <v>612.76</v>
       </c>
       <c r="F26" s="24">
         <f>IFERROR(VLOOKUP($B26,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -2992,29 +3028,29 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="22" customHeight="1">
+    <row r="27" ht="33" customHeight="1">
       <c r="A27" s="21" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F27" s="24">
         <f>IFERROR(VLOOKUP($B27,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3028,26 +3064,26 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="21" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E28" s="23" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F28" s="24">
         <f>IFERROR(VLOOKUP($B28,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3059,15 +3095,19 @@
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="25" t="n"/>
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>30.100.2105</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -3087,16 +3127,16 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="14" customHeight="1">
+    <row r="30" ht="22" customHeight="1">
       <c r="A30" s="25" t="n"/>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -3105,7 +3145,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="24">
         <f>IFERROR(VLOOKUP($B30,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3116,25 +3156,25 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="22" customHeight="1">
+    <row r="31" ht="14" customHeight="1">
       <c r="A31" s="25" t="n"/>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="F31" s="24">
         <f>IFERROR(VLOOKUP($B31,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3149,21 +3189,21 @@
       <c r="A32" s="25" t="n"/>
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="F32" s="24">
         <f>IFERROR(VLOOKUP($B32,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3178,12 +3218,12 @@
       <c r="A33" s="25" t="n"/>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -3192,7 +3232,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F33" s="24">
         <f>IFERROR(VLOOKUP($B33,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3203,25 +3243,25 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="14" customHeight="1">
+    <row r="34" ht="22" customHeight="1">
       <c r="A34" s="25" t="n"/>
       <c r="B34" s="22" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="F34" s="24">
         <f>IFERROR(VLOOKUP($B34,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3232,16 +3272,16 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
+    <row r="35" ht="14" customHeight="1">
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -3250,7 +3290,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="F35" s="24">
         <f>IFERROR(VLOOKUP($B35,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3265,12 +3305,12 @@
       <c r="A36" s="25" t="n"/>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -3279,7 +3319,7 @@
         </is>
       </c>
       <c r="E36" s="23" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="F36" s="24">
         <f>IFERROR(VLOOKUP($B36,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3294,12 +3334,12 @@
       <c r="A37" s="25" t="n"/>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -3308,7 +3348,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F37" s="24">
         <f>IFERROR(VLOOKUP($B37,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3323,12 +3363,12 @@
       <c r="A38" s="25" t="n"/>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -3337,7 +3377,7 @@
         </is>
       </c>
       <c r="E38" s="23" t="n">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="F38" s="24">
         <f>IFERROR(VLOOKUP($B38,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3352,21 +3392,21 @@
       <c r="A39" s="25" t="n"/>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="F39" s="24">
         <f>IFERROR(VLOOKUP($B39,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3381,21 +3421,21 @@
       <c r="A40" s="25" t="n"/>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E40" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F40" s="24">
         <f>IFERROR(VLOOKUP($B40,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3410,21 +3450,21 @@
       <c r="A41" s="25" t="n"/>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F41" s="24">
         <f>IFERROR(VLOOKUP($B41,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3435,16 +3475,16 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="14" customHeight="1">
-      <c r="A42" s="26" t="n"/>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="25" t="n"/>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -3464,33 +3504,63 @@
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="11" t="n"/>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="27" t="inlineStr">
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="26" t="n"/>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>30.740.5406</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="24">
+        <f>IFERROR(VLOOKUP($B43,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G43" s="5">
+        <f>E43*F43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
-      <c r="G43" s="13">
-        <f>SUM(G6:G42)</f>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="13">
+        <f>SUM(G6:G43)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A29:A43"/>
     <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A28:A42"/>
+    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3502,7 +3572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3963,7 +4033,7 @@
         </is>
       </c>
       <c r="E18" s="23" t="n">
-        <v>360.16</v>
+        <v>319.2</v>
       </c>
       <c r="F18" s="24">
         <f>IFERROR(VLOOKUP($B18,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3974,29 +4044,25 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="33" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
-        </is>
-      </c>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="26" t="n"/>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>13.4</v>
+        <v>51.2</v>
       </c>
       <c r="F19" s="24">
         <f>IFERROR(VLOOKUP($B19,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4007,16 +4073,20 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="25" t="n"/>
+    <row r="20" ht="33" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+        </is>
+      </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -4025,7 +4095,7 @@
         </is>
       </c>
       <c r="E20" s="23" t="n">
-        <v>5.67</v>
+        <v>13.4</v>
       </c>
       <c r="F20" s="24">
         <f>IFERROR(VLOOKUP($B20,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4037,24 +4107,24 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="26" t="n"/>
+      <c r="A21" s="25" t="n"/>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>54.315</v>
+        <v>5.67</v>
       </c>
       <c r="F21" s="24">
         <f>IFERROR(VLOOKUP($B21,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4065,29 +4135,25 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="21" t="inlineStr">
-        <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
-        </is>
-      </c>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="26" t="n"/>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E22" s="23" t="n">
-        <v>557.76</v>
+        <v>54.315</v>
       </c>
       <c r="F22" s="24">
         <f>IFERROR(VLOOKUP($B22,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4098,16 +4164,20 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="26" t="n"/>
+    <row r="23" ht="14" customHeight="1">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Sıva, alçı, derz ve şap işleri</t>
+        </is>
+      </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -4116,7 +4186,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>647.76</v>
+        <v>557.76</v>
       </c>
       <c r="F23" s="24">
         <f>IFERROR(VLOOKUP($B23,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4128,19 +4198,15 @@
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>Boya, badana ve cila işleri</t>
-        </is>
-      </c>
+      <c r="A24" s="26" t="n"/>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -4149,7 +4215,7 @@
         </is>
       </c>
       <c r="E24" s="23" t="n">
-        <v>557.76</v>
+        <v>647.76</v>
       </c>
       <c r="F24" s="24">
         <f>IFERROR(VLOOKUP($B24,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4161,15 +4227,19 @@
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="26" t="n"/>
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Boya, badana ve cila işleri</t>
+        </is>
+      </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -4178,7 +4248,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>612.76</v>
+        <v>557.76</v>
       </c>
       <c r="F25" s="24">
         <f>IFERROR(VLOOKUP($B25,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4189,20 +4259,16 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="33" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
-        </is>
-      </c>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="26" t="n"/>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -4211,7 +4277,7 @@
         </is>
       </c>
       <c r="E26" s="23" t="n">
-        <v>60</v>
+        <v>612.76</v>
       </c>
       <c r="F26" s="24">
         <f>IFERROR(VLOOKUP($B26,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4222,29 +4288,29 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="22" customHeight="1">
+    <row r="27" ht="33" customHeight="1">
       <c r="A27" s="21" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F27" s="24">
         <f>IFERROR(VLOOKUP($B27,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4258,26 +4324,26 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="21" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E28" s="23" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F28" s="24">
         <f>IFERROR(VLOOKUP($B28,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4289,15 +4355,19 @@
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="25" t="n"/>
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>30.100.2105</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -4317,16 +4387,16 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="14" customHeight="1">
+    <row r="30" ht="22" customHeight="1">
       <c r="A30" s="25" t="n"/>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4335,7 +4405,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="24">
         <f>IFERROR(VLOOKUP($B30,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4346,25 +4416,25 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="22" customHeight="1">
+    <row r="31" ht="14" customHeight="1">
       <c r="A31" s="25" t="n"/>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="F31" s="24">
         <f>IFERROR(VLOOKUP($B31,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4379,21 +4449,21 @@
       <c r="A32" s="25" t="n"/>
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="F32" s="24">
         <f>IFERROR(VLOOKUP($B32,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4408,12 +4478,12 @@
       <c r="A33" s="25" t="n"/>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4422,7 +4492,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F33" s="24">
         <f>IFERROR(VLOOKUP($B33,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4433,25 +4503,25 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="14" customHeight="1">
+    <row r="34" ht="22" customHeight="1">
       <c r="A34" s="25" t="n"/>
       <c r="B34" s="22" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="F34" s="24">
         <f>IFERROR(VLOOKUP($B34,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4462,16 +4532,16 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
+    <row r="35" ht="14" customHeight="1">
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -4480,7 +4550,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="F35" s="24">
         <f>IFERROR(VLOOKUP($B35,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4495,12 +4565,12 @@
       <c r="A36" s="25" t="n"/>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -4509,7 +4579,7 @@
         </is>
       </c>
       <c r="E36" s="23" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="F36" s="24">
         <f>IFERROR(VLOOKUP($B36,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4524,12 +4594,12 @@
       <c r="A37" s="25" t="n"/>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -4538,7 +4608,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F37" s="24">
         <f>IFERROR(VLOOKUP($B37,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4553,12 +4623,12 @@
       <c r="A38" s="25" t="n"/>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -4567,7 +4637,7 @@
         </is>
       </c>
       <c r="E38" s="23" t="n">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="F38" s="24">
         <f>IFERROR(VLOOKUP($B38,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4582,21 +4652,21 @@
       <c r="A39" s="25" t="n"/>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="F39" s="24">
         <f>IFERROR(VLOOKUP($B39,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4611,21 +4681,21 @@
       <c r="A40" s="25" t="n"/>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E40" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F40" s="24">
         <f>IFERROR(VLOOKUP($B40,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4640,21 +4710,21 @@
       <c r="A41" s="25" t="n"/>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F41" s="24">
         <f>IFERROR(VLOOKUP($B41,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4665,16 +4735,16 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="14" customHeight="1">
-      <c r="A42" s="26" t="n"/>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="25" t="n"/>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -4694,33 +4764,63 @@
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="11" t="n"/>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="27" t="inlineStr">
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="26" t="n"/>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>30.740.5406</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="24">
+        <f>IFERROR(VLOOKUP($B43,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G43" s="5">
+        <f>E43*F43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
-      <c r="G43" s="13">
-        <f>SUM(G6:G42)</f>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="13">
+        <f>SUM(G6:G43)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A29:A43"/>
     <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A28:A42"/>
+    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="C4" s="5">
-        <f>'01 Kümes A Blok'!$G$44</f>
+        <f>'01 Kümes A Blok'!$G$42</f>
         <v/>
       </c>
       <c r="D4" s="6">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>'02 Kümes B Blok'!$G$44</f>
+        <f>'02 Kümes B Blok'!$G$42</f>
         <v/>
       </c>
       <c r="D5" s="6">
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1897,15 +1897,15 @@
         <v>1996.08</v>
       </c>
     </row>
-    <row r="34" ht="33" customHeight="1">
+    <row r="34" ht="22" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>556368.2</v>
+        <v>18566.2</v>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
@@ -1934,27 +1934,27 @@
         <v/>
       </c>
       <c r="I34" s="13" t="n">
-        <v>467349.29</v>
+        <v>15595.61</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>94825.64999999999</v>
+        <v>508</v>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
@@ -1974,27 +1974,27 @@
         <v/>
       </c>
       <c r="I35" s="13" t="n">
-        <v>79653.55</v>
+        <v>426.72</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>18566.2</v>
+        <v>138.05</v>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
@@ -2014,18 +2014,18 @@
         <v/>
       </c>
       <c r="I36" s="13" t="n">
-        <v>15595.61</v>
+        <v>115.96</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2034,11 +2034,11 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>508</v>
+        <v>393.69</v>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F37" s="20">
@@ -2054,31 +2054,31 @@
         <v/>
       </c>
       <c r="I37" s="13" t="n">
-        <v>426.72</v>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
+        <v>330.7</v>
+      </c>
+    </row>
+    <row r="38" ht="14" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>138.05</v>
+        <v>271.25</v>
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F38" s="20">
@@ -2094,27 +2094,27 @@
         <v/>
       </c>
       <c r="I38" s="13" t="n">
-        <v>115.96</v>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
+        <v>227.85</v>
+      </c>
+    </row>
+    <row r="39" ht="33" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>393.69</v>
+        <v>1035.88</v>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
@@ -2134,27 +2134,27 @@
         <v/>
       </c>
       <c r="I39" s="13" t="n">
-        <v>330.7</v>
-      </c>
-    </row>
-    <row r="40" ht="14" customHeight="1">
+        <v>870.14</v>
+      </c>
+    </row>
+    <row r="40" ht="33" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>271.25</v>
+        <v>3199.68</v>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
@@ -2174,18 +2174,18 @@
         <v/>
       </c>
       <c r="I40" s="13" t="n">
-        <v>227.85</v>
-      </c>
-    </row>
-    <row r="41" ht="33" customHeight="1">
+        <v>2687.73</v>
+      </c>
+    </row>
+    <row r="41" ht="44" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1035.88</v>
+        <v>835.1</v>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
@@ -2214,86 +2214,6 @@
         <v/>
       </c>
       <c r="I41" s="13" t="n">
-        <v>870.14</v>
-      </c>
-    </row>
-    <row r="42" ht="33" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0175</t>
-        </is>
-      </c>
-      <c r="B42" s="18" t="inlineStr">
-        <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>3199.68</v>
-      </c>
-      <c r="E42" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F42" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G42" s="5">
-        <f>D42*(1-F42)</f>
-        <v/>
-      </c>
-      <c r="H42" s="5">
-        <f>D42*$D$3</f>
-        <v/>
-      </c>
-      <c r="I42" s="13" t="n">
-        <v>2687.73</v>
-      </c>
-    </row>
-    <row r="43" ht="44" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0177</t>
-        </is>
-      </c>
-      <c r="B43" s="18" t="inlineStr">
-        <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>835.1</v>
-      </c>
-      <c r="E43" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F43" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G43" s="5">
-        <f>D43*(1-F43)</f>
-        <v/>
-      </c>
-      <c r="H43" s="5">
-        <f>D43*$D$3</f>
-        <v/>
-      </c>
-      <c r="I43" s="13" t="n">
         <v>701.48</v>
       </c>
     </row>
@@ -2312,7 +2232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3447,7 +3367,7 @@
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="25" t="n"/>
+      <c r="A41" s="26" t="n"/>
       <c r="B41" s="22" t="inlineStr">
         <is>
           <t>30.750.2001</t>
@@ -3475,88 +3395,30 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="25" t="n"/>
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>30.740.1106</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="inlineStr">
-        <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E42" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="24">
-        <f>IFERROR(VLOOKUP($B42,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G42" s="5">
-        <f>E42*F42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="26" t="n"/>
-      <c r="B43" s="22" t="inlineStr">
-        <is>
-          <t>30.740.5406</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="24">
-        <f>IFERROR(VLOOKUP($B43,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G43" s="5">
-        <f>E43*F43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="n"/>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="27" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="n"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="13">
-        <f>SUM(G6:G43)</f>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="13">
+        <f>SUM(G6:G41)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A29:A43"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A29:A41"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A23:A24"/>
@@ -3572,7 +3434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4707,7 +4569,7 @@
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="25" t="n"/>
+      <c r="A41" s="26" t="n"/>
       <c r="B41" s="22" t="inlineStr">
         <is>
           <t>30.750.2001</t>
@@ -4735,88 +4597,30 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="25" t="n"/>
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>30.740.1106</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="inlineStr">
-        <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E42" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="24">
-        <f>IFERROR(VLOOKUP($B42,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G42" s="5">
-        <f>E42*F42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="26" t="n"/>
-      <c r="B43" s="22" t="inlineStr">
-        <is>
-          <t>30.740.5406</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="24">
-        <f>IFERROR(VLOOKUP($B43,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G43" s="5">
-        <f>E43*F43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="n"/>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="27" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="n"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="13">
-        <f>SUM(G6:G43)</f>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="13">
+        <f>SUM(G6:G41)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A29:A43"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A29:A41"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A23:A24"/>

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>31.4285</v>
+        <v>31.428</v>
       </c>
       <c r="F7" s="24">
         <f>IFERROR(VLOOKUP($B7,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="E10" s="23" t="n">
-        <v>4.1599</v>
+        <v>4.16</v>
       </c>
       <c r="F10" s="24">
         <f>IFERROR(VLOOKUP($B10,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>7.2875</v>
+        <v>7.287</v>
       </c>
       <c r="F11" s="24">
         <f>IFERROR(VLOOKUP($B11,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="E12" s="23" t="n">
-        <v>3.6375</v>
+        <v>3.637</v>
       </c>
       <c r="F12" s="24">
         <f>IFERROR(VLOOKUP($B12,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>44.0481</v>
+        <v>44.048</v>
       </c>
       <c r="F13" s="24">
         <f>IFERROR(VLOOKUP($B13,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>31.4285</v>
+        <v>31.428</v>
       </c>
       <c r="F7" s="24">
         <f>IFERROR(VLOOKUP($B7,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="E10" s="23" t="n">
-        <v>4.1599</v>
+        <v>4.16</v>
       </c>
       <c r="F10" s="24">
         <f>IFERROR(VLOOKUP($B10,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>7.2875</v>
+        <v>7.287</v>
       </c>
       <c r="F11" s="24">
         <f>IFERROR(VLOOKUP($B11,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="E12" s="23" t="n">
-        <v>3.6375</v>
+        <v>3.637</v>
       </c>
       <c r="F12" s="24">
         <f>IFERROR(VLOOKUP($B12,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>44.0481</v>
+        <v>44.048</v>
       </c>
       <c r="F13" s="24">
         <f>IFERROR(VLOOKUP($B13,'Fiyatlar'!$A:$I,9,FALSE),0)</f>

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="C4" s="5">
-        <f>'01 Kümes A Blok'!$G$42</f>
+        <f>'01 Kümes A Blok'!$G$44</f>
         <v/>
       </c>
       <c r="D4" s="6">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>'02 Kümes B Blok'!$G$42</f>
+        <f>'02 Kümes B Blok'!$G$44</f>
         <v/>
       </c>
       <c r="D5" s="6">
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1897,15 +1897,15 @@
         <v>1996.08</v>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
+    <row r="34" ht="33" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>18566.2</v>
+        <v>556368.2</v>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
@@ -1934,27 +1934,27 @@
         <v/>
       </c>
       <c r="I34" s="13" t="n">
-        <v>15595.61</v>
+        <v>467349.29</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>30.740.5406</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>508</v>
+        <v>94825.64999999999</v>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
@@ -1974,27 +1974,27 @@
         <v/>
       </c>
       <c r="I35" s="13" t="n">
-        <v>426.72</v>
+        <v>79653.55</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>138.05</v>
+        <v>18566.2</v>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
@@ -2014,18 +2014,18 @@
         <v/>
       </c>
       <c r="I36" s="13" t="n">
-        <v>115.96</v>
+        <v>15595.61</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2034,11 +2034,11 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>393.69</v>
+        <v>508</v>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F37" s="20">
@@ -2054,31 +2054,31 @@
         <v/>
       </c>
       <c r="I37" s="13" t="n">
-        <v>330.7</v>
-      </c>
-    </row>
-    <row r="38" ht="14" customHeight="1">
+        <v>426.72</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>271.25</v>
+        <v>138.05</v>
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F38" s="20">
@@ -2094,27 +2094,27 @@
         <v/>
       </c>
       <c r="I38" s="13" t="n">
-        <v>227.85</v>
-      </c>
-    </row>
-    <row r="39" ht="33" customHeight="1">
+        <v>115.96</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>1035.88</v>
+        <v>393.69</v>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
@@ -2134,27 +2134,27 @@
         <v/>
       </c>
       <c r="I39" s="13" t="n">
-        <v>870.14</v>
-      </c>
-    </row>
-    <row r="40" ht="33" customHeight="1">
+        <v>330.7</v>
+      </c>
+    </row>
+    <row r="40" ht="14" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>3199.68</v>
+        <v>271.25</v>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
@@ -2174,18 +2174,18 @@
         <v/>
       </c>
       <c r="I40" s="13" t="n">
-        <v>2687.73</v>
-      </c>
-    </row>
-    <row r="41" ht="44" customHeight="1">
+        <v>227.85</v>
+      </c>
+    </row>
+    <row r="41" ht="33" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>835.1</v>
+        <v>1035.88</v>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
@@ -2214,6 +2214,86 @@
         <v/>
       </c>
       <c r="I41" s="13" t="n">
+        <v>870.14</v>
+      </c>
+    </row>
+    <row r="42" ht="33" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>TKDK-0175</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>3199.68</v>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F42" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G42" s="5">
+        <f>D42*(1-F42)</f>
+        <v/>
+      </c>
+      <c r="H42" s="5">
+        <f>D42*$D$3</f>
+        <v/>
+      </c>
+      <c r="I42" s="13" t="n">
+        <v>2687.73</v>
+      </c>
+    </row>
+    <row r="43" ht="44" customHeight="1">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>TKDK-0177</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>835.1</v>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F43" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G43" s="5">
+        <f>D43*(1-F43)</f>
+        <v/>
+      </c>
+      <c r="H43" s="5">
+        <f>D43*$D$3</f>
+        <v/>
+      </c>
+      <c r="I43" s="13" t="n">
         <v>701.48</v>
       </c>
     </row>
@@ -2232,7 +2312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3367,7 +3447,7 @@
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="26" t="n"/>
+      <c r="A41" s="25" t="n"/>
       <c r="B41" s="22" t="inlineStr">
         <is>
           <t>30.750.2001</t>
@@ -3395,30 +3475,88 @@
         <v/>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="11" t="n"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="27" t="inlineStr">
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="25" t="n"/>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>30.740.1106</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="24">
+        <f>IFERROR(VLOOKUP($B42,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G42" s="5">
+        <f>E42*F42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="26" t="n"/>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>30.740.5406</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="24">
+        <f>IFERROR(VLOOKUP($B43,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G43" s="5">
+        <f>E43*F43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
-      <c r="G42" s="13">
-        <f>SUM(G6:G41)</f>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="13">
+        <f>SUM(G6:G43)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A29:A43"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A29:A41"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A23:A24"/>
@@ -3434,7 +3572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4569,7 +4707,7 @@
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="26" t="n"/>
+      <c r="A41" s="25" t="n"/>
       <c r="B41" s="22" t="inlineStr">
         <is>
           <t>30.750.2001</t>
@@ -4597,30 +4735,88 @@
         <v/>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="11" t="n"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="27" t="inlineStr">
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="25" t="n"/>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>30.740.1106</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="24">
+        <f>IFERROR(VLOOKUP($B42,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G42" s="5">
+        <f>E42*F42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="26" t="n"/>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>30.740.5406</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="24">
+        <f>IFERROR(VLOOKUP($B43,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G43" s="5">
+        <f>E43*F43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
-      <c r="G42" s="13">
-        <f>SUM(G6:G41)</f>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="13">
+        <f>SUM(G6:G43)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A29:A43"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A29:A41"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A23:A24"/>

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>31.428</v>
+        <v>31.429</v>
       </c>
       <c r="F7" s="24">
         <f>IFERROR(VLOOKUP($B7,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>7.287</v>
+        <v>7.288</v>
       </c>
       <c r="F11" s="24">
         <f>IFERROR(VLOOKUP($B11,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>31.428</v>
+        <v>31.429</v>
       </c>
       <c r="F7" s="24">
         <f>IFERROR(VLOOKUP($B7,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>7.287</v>
+        <v>7.288</v>
       </c>
       <c r="F11" s="24">
         <f>IFERROR(VLOOKUP($B11,'Fiyatlar'!$A:$I,9,FALSE),0)</f>

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="C4" s="5">
-        <f>'01 Kümes A Blok'!$G$44</f>
+        <f>'01 Kümes A Blok'!$G$46</f>
         <v/>
       </c>
       <c r="D4" s="6">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>'02 Kümes B Blok'!$G$44</f>
+        <f>'02 Kümes B Blok'!$G$46</f>
         <v/>
       </c>
       <c r="D5" s="6">
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2100,25 +2100,25 @@
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>393.69</v>
+        <v>237.4</v>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F39" s="20">
@@ -2134,18 +2134,18 @@
         <v/>
       </c>
       <c r="I39" s="13" t="n">
-        <v>330.7</v>
-      </c>
-    </row>
-    <row r="40" ht="14" customHeight="1">
+        <v>199.42</v>
+      </c>
+    </row>
+    <row r="40" ht="33" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>35.190.1100 (montaj)</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2154,11 +2154,11 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>271.25</v>
+        <v>46.09</v>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 35.190.1100 pozunun 01.06.2026 tarihli MONTAJ fiyatı 46,09 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 189,92 x 1,25 + montaj 46,09 = 283,49 TL</t>
         </is>
       </c>
       <c r="F40" s="20">
@@ -2174,27 +2174,27 @@
         <v/>
       </c>
       <c r="I40" s="13" t="n">
-        <v>227.85</v>
-      </c>
-    </row>
-    <row r="41" ht="33" customHeight="1">
+        <v>38.72</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1035.88</v>
+        <v>393.69</v>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
@@ -2214,27 +2214,27 @@
         <v/>
       </c>
       <c r="I41" s="13" t="n">
-        <v>870.14</v>
-      </c>
-    </row>
-    <row r="42" ht="33" customHeight="1">
+        <v>330.7</v>
+      </c>
+    </row>
+    <row r="42" ht="14" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>3199.68</v>
+        <v>271.25</v>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
@@ -2254,18 +2254,18 @@
         <v/>
       </c>
       <c r="I42" s="13" t="n">
-        <v>2687.73</v>
-      </c>
-    </row>
-    <row r="43" ht="44" customHeight="1">
+        <v>227.85</v>
+      </c>
+    </row>
+    <row r="43" ht="33" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>835.1</v>
+        <v>1035.88</v>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
@@ -2294,6 +2294,86 @@
         <v/>
       </c>
       <c r="I43" s="13" t="n">
+        <v>870.14</v>
+      </c>
+    </row>
+    <row r="44" ht="33" customHeight="1">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>TKDK-0175</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>3199.68</v>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F44" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G44" s="5">
+        <f>D44*(1-F44)</f>
+        <v/>
+      </c>
+      <c r="H44" s="5">
+        <f>D44*$D$3</f>
+        <v/>
+      </c>
+      <c r="I44" s="13" t="n">
+        <v>2687.73</v>
+      </c>
+    </row>
+    <row r="45" ht="44" customHeight="1">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>TKDK-0177</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>835.1</v>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F45" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G45" s="5">
+        <f>D45*(1-F45)</f>
+        <v/>
+      </c>
+      <c r="H45" s="5">
+        <f>D45*$D$3</f>
+        <v/>
+      </c>
+      <c r="I45" s="13" t="n">
         <v>701.48</v>
       </c>
     </row>
@@ -2312,7 +2392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3505,7 +3585,7 @@
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="26" t="n"/>
+      <c r="A43" s="25" t="n"/>
       <c r="B43" s="22" t="inlineStr">
         <is>
           <t>30.740.5406</t>
@@ -3533,29 +3613,87 @@
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="n"/>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="27" t="inlineStr">
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="25" t="n"/>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="n">
+        <v>502</v>
+      </c>
+      <c r="F44" s="24">
+        <f>IFERROR(VLOOKUP($B44,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G44" s="5">
+        <f>E44*F44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="33" customHeight="1">
+      <c r="A45" s="26" t="n"/>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="n">
+        <v>502</v>
+      </c>
+      <c r="F45" s="24">
+        <f>IFERROR(VLOOKUP($B45,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G45" s="5">
+        <f>E45*F45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="n"/>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="13">
-        <f>SUM(G6:G43)</f>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
+      <c r="G46" s="13">
+        <f>SUM(G6:G45)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A29:A43"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A29:A45"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
@@ -3572,7 +3710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4765,7 +4903,7 @@
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="26" t="n"/>
+      <c r="A43" s="25" t="n"/>
       <c r="B43" s="22" t="inlineStr">
         <is>
           <t>30.740.5406</t>
@@ -4793,29 +4931,87 @@
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="n"/>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="27" t="inlineStr">
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="25" t="n"/>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="n">
+        <v>502</v>
+      </c>
+      <c r="F44" s="24">
+        <f>IFERROR(VLOOKUP($B44,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G44" s="5">
+        <f>E44*F44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="33" customHeight="1">
+      <c r="A45" s="26" t="n"/>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="n">
+        <v>502</v>
+      </c>
+      <c r="F45" s="24">
+        <f>IFERROR(VLOOKUP($B45,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G45" s="5">
+        <f>E45*F45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="n"/>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="13">
-        <f>SUM(G6:G43)</f>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
+      <c r="G46" s="13">
+        <f>SUM(G6:G45)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A29:A43"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A29:A45"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="C4" s="5">
-        <f>'01 Kümes A Blok'!$G$46</f>
+        <f>'01 Kümes A Blok'!$G$48</f>
         <v/>
       </c>
       <c r="D4" s="6">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>'02 Kümes B Blok'!$G$46</f>
+        <f>'02 Kümes B Blok'!$G$48</f>
         <v/>
       </c>
       <c r="D5" s="6">
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2177,28 +2177,28 @@
         <v>38.72</v>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1">
+    <row r="41" ht="33" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>393.69</v>
+        <v>193.3</v>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F41" s="20">
@@ -2214,18 +2214,18 @@
         <v/>
       </c>
       <c r="I41" s="13" t="n">
-        <v>330.7</v>
-      </c>
-    </row>
-    <row r="42" ht="14" customHeight="1">
+        <v>162.37</v>
+      </c>
+    </row>
+    <row r="42" ht="33" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>35.190.1101 (montaj)</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2234,11 +2234,11 @@
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>271.25</v>
+        <v>25.36</v>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 35.190.1101 pozunun 01.06.2026 tarihli MONTAJ fiyatı 25,36 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 154,64 x 1,25 + montaj 25,36 = 218,66 TL</t>
         </is>
       </c>
       <c r="F42" s="20">
@@ -2254,27 +2254,27 @@
         <v/>
       </c>
       <c r="I42" s="13" t="n">
-        <v>227.85</v>
-      </c>
-    </row>
-    <row r="43" ht="33" customHeight="1">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>1035.88</v>
+        <v>393.69</v>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
@@ -2294,27 +2294,27 @@
         <v/>
       </c>
       <c r="I43" s="13" t="n">
-        <v>870.14</v>
-      </c>
-    </row>
-    <row r="44" ht="33" customHeight="1">
+        <v>330.7</v>
+      </c>
+    </row>
+    <row r="44" ht="14" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>3199.68</v>
+        <v>271.25</v>
       </c>
       <c r="E44" s="19" t="inlineStr">
         <is>
@@ -2334,18 +2334,18 @@
         <v/>
       </c>
       <c r="I44" s="13" t="n">
-        <v>2687.73</v>
-      </c>
-    </row>
-    <row r="45" ht="44" customHeight="1">
+        <v>227.85</v>
+      </c>
+    </row>
+    <row r="45" ht="33" customHeight="1">
       <c r="A45" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>835.1</v>
+        <v>1035.88</v>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
@@ -2374,6 +2374,86 @@
         <v/>
       </c>
       <c r="I45" s="13" t="n">
+        <v>870.14</v>
+      </c>
+    </row>
+    <row r="46" ht="33" customHeight="1">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>TKDK-0175</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>3199.68</v>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F46" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G46" s="5">
+        <f>D46*(1-F46)</f>
+        <v/>
+      </c>
+      <c r="H46" s="5">
+        <f>D46*$D$3</f>
+        <v/>
+      </c>
+      <c r="I46" s="13" t="n">
+        <v>2687.73</v>
+      </c>
+    </row>
+    <row r="47" ht="44" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>TKDK-0177</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>835.1</v>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F47" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G47" s="5">
+        <f>D47*(1-F47)</f>
+        <v/>
+      </c>
+      <c r="H47" s="5">
+        <f>D47*$D$3</f>
+        <v/>
+      </c>
+      <c r="I47" s="13" t="n">
         <v>701.48</v>
       </c>
     </row>
@@ -2392,7 +2472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2484,7 +2564,7 @@
         <v/>
       </c>
       <c r="G6" s="5">
-        <f>E6*F6</f>
+        <f>ROUND(E6*F6,2)</f>
         <v/>
       </c>
     </row>
@@ -2517,7 +2597,7 @@
         <v/>
       </c>
       <c r="G7" s="5">
-        <f>E7*F7</f>
+        <f>ROUND(E7*F7,2)</f>
         <v/>
       </c>
     </row>
@@ -2550,7 +2630,7 @@
         <v/>
       </c>
       <c r="G8" s="5">
-        <f>E8*F8</f>
+        <f>ROUND(E8*F8,2)</f>
         <v/>
       </c>
     </row>
@@ -2583,7 +2663,7 @@
         <v/>
       </c>
       <c r="G9" s="5">
-        <f>E9*F9</f>
+        <f>ROUND(E9*F9,2)</f>
         <v/>
       </c>
     </row>
@@ -2616,7 +2696,7 @@
         <v/>
       </c>
       <c r="G10" s="5">
-        <f>E10*F10</f>
+        <f>ROUND(E10*F10,2)</f>
         <v/>
       </c>
     </row>
@@ -2645,7 +2725,7 @@
         <v/>
       </c>
       <c r="G11" s="5">
-        <f>E11*F11</f>
+        <f>ROUND(E11*F11,2)</f>
         <v/>
       </c>
     </row>
@@ -2674,7 +2754,7 @@
         <v/>
       </c>
       <c r="G12" s="5">
-        <f>E12*F12</f>
+        <f>ROUND(E12*F12,2)</f>
         <v/>
       </c>
     </row>
@@ -2707,7 +2787,7 @@
         <v/>
       </c>
       <c r="G13" s="5">
-        <f>E13*F13</f>
+        <f>ROUND(E13*F13,2)</f>
         <v/>
       </c>
     </row>
@@ -2736,7 +2816,7 @@
         <v/>
       </c>
       <c r="G14" s="5">
-        <f>E14*F14</f>
+        <f>ROUND(E14*F14,2)</f>
         <v/>
       </c>
     </row>
@@ -2769,7 +2849,7 @@
         <v/>
       </c>
       <c r="G15" s="5">
-        <f>E15*F15</f>
+        <f>ROUND(E15*F15,2)</f>
         <v/>
       </c>
     </row>
@@ -2798,7 +2878,7 @@
         <v/>
       </c>
       <c r="G16" s="5">
-        <f>E16*F16</f>
+        <f>ROUND(E16*F16,2)</f>
         <v/>
       </c>
     </row>
@@ -2827,7 +2907,7 @@
         <v/>
       </c>
       <c r="G17" s="5">
-        <f>E17*F17</f>
+        <f>ROUND(E17*F17,2)</f>
         <v/>
       </c>
     </row>
@@ -2860,7 +2940,7 @@
         <v/>
       </c>
       <c r="G18" s="5">
-        <f>E18*F18</f>
+        <f>ROUND(E18*F18,2)</f>
         <v/>
       </c>
     </row>
@@ -2889,7 +2969,7 @@
         <v/>
       </c>
       <c r="G19" s="5">
-        <f>E19*F19</f>
+        <f>ROUND(E19*F19,2)</f>
         <v/>
       </c>
     </row>
@@ -2922,7 +3002,7 @@
         <v/>
       </c>
       <c r="G20" s="5">
-        <f>E20*F20</f>
+        <f>ROUND(E20*F20,2)</f>
         <v/>
       </c>
     </row>
@@ -2951,7 +3031,7 @@
         <v/>
       </c>
       <c r="G21" s="5">
-        <f>E21*F21</f>
+        <f>ROUND(E21*F21,2)</f>
         <v/>
       </c>
     </row>
@@ -2980,7 +3060,7 @@
         <v/>
       </c>
       <c r="G22" s="5">
-        <f>E22*F22</f>
+        <f>ROUND(E22*F22,2)</f>
         <v/>
       </c>
     </row>
@@ -3013,7 +3093,7 @@
         <v/>
       </c>
       <c r="G23" s="5">
-        <f>E23*F23</f>
+        <f>ROUND(E23*F23,2)</f>
         <v/>
       </c>
     </row>
@@ -3042,7 +3122,7 @@
         <v/>
       </c>
       <c r="G24" s="5">
-        <f>E24*F24</f>
+        <f>ROUND(E24*F24,2)</f>
         <v/>
       </c>
     </row>
@@ -3075,7 +3155,7 @@
         <v/>
       </c>
       <c r="G25" s="5">
-        <f>E25*F25</f>
+        <f>ROUND(E25*F25,2)</f>
         <v/>
       </c>
     </row>
@@ -3104,7 +3184,7 @@
         <v/>
       </c>
       <c r="G26" s="5">
-        <f>E26*F26</f>
+        <f>ROUND(E26*F26,2)</f>
         <v/>
       </c>
     </row>
@@ -3137,7 +3217,7 @@
         <v/>
       </c>
       <c r="G27" s="5">
-        <f>E27*F27</f>
+        <f>ROUND(E27*F27,2)</f>
         <v/>
       </c>
     </row>
@@ -3170,7 +3250,7 @@
         <v/>
       </c>
       <c r="G28" s="5">
-        <f>E28*F28</f>
+        <f>ROUND(E28*F28,2)</f>
         <v/>
       </c>
     </row>
@@ -3203,7 +3283,7 @@
         <v/>
       </c>
       <c r="G29" s="5">
-        <f>E29*F29</f>
+        <f>ROUND(E29*F29,2)</f>
         <v/>
       </c>
     </row>
@@ -3232,7 +3312,7 @@
         <v/>
       </c>
       <c r="G30" s="5">
-        <f>E30*F30</f>
+        <f>ROUND(E30*F30,2)</f>
         <v/>
       </c>
     </row>
@@ -3261,7 +3341,7 @@
         <v/>
       </c>
       <c r="G31" s="5">
-        <f>E31*F31</f>
+        <f>ROUND(E31*F31,2)</f>
         <v/>
       </c>
     </row>
@@ -3290,7 +3370,7 @@
         <v/>
       </c>
       <c r="G32" s="5">
-        <f>E32*F32</f>
+        <f>ROUND(E32*F32,2)</f>
         <v/>
       </c>
     </row>
@@ -3319,7 +3399,7 @@
         <v/>
       </c>
       <c r="G33" s="5">
-        <f>E33*F33</f>
+        <f>ROUND(E33*F33,2)</f>
         <v/>
       </c>
     </row>
@@ -3348,7 +3428,7 @@
         <v/>
       </c>
       <c r="G34" s="5">
-        <f>E34*F34</f>
+        <f>ROUND(E34*F34,2)</f>
         <v/>
       </c>
     </row>
@@ -3377,7 +3457,7 @@
         <v/>
       </c>
       <c r="G35" s="5">
-        <f>E35*F35</f>
+        <f>ROUND(E35*F35,2)</f>
         <v/>
       </c>
     </row>
@@ -3406,7 +3486,7 @@
         <v/>
       </c>
       <c r="G36" s="5">
-        <f>E36*F36</f>
+        <f>ROUND(E36*F36,2)</f>
         <v/>
       </c>
     </row>
@@ -3435,7 +3515,7 @@
         <v/>
       </c>
       <c r="G37" s="5">
-        <f>E37*F37</f>
+        <f>ROUND(E37*F37,2)</f>
         <v/>
       </c>
     </row>
@@ -3464,7 +3544,7 @@
         <v/>
       </c>
       <c r="G38" s="5">
-        <f>E38*F38</f>
+        <f>ROUND(E38*F38,2)</f>
         <v/>
       </c>
     </row>
@@ -3493,7 +3573,7 @@
         <v/>
       </c>
       <c r="G39" s="5">
-        <f>E39*F39</f>
+        <f>ROUND(E39*F39,2)</f>
         <v/>
       </c>
     </row>
@@ -3522,7 +3602,7 @@
         <v/>
       </c>
       <c r="G40" s="5">
-        <f>E40*F40</f>
+        <f>ROUND(E40*F40,2)</f>
         <v/>
       </c>
     </row>
@@ -3551,7 +3631,7 @@
         <v/>
       </c>
       <c r="G41" s="5">
-        <f>E41*F41</f>
+        <f>ROUND(E41*F41,2)</f>
         <v/>
       </c>
     </row>
@@ -3580,7 +3660,7 @@
         <v/>
       </c>
       <c r="G42" s="5">
-        <f>E42*F42</f>
+        <f>ROUND(E42*F42,2)</f>
         <v/>
       </c>
     </row>
@@ -3609,7 +3689,7 @@
         <v/>
       </c>
       <c r="G43" s="5">
-        <f>E43*F43</f>
+        <f>ROUND(E43*F43,2)</f>
         <v/>
       </c>
     </row>
@@ -3638,12 +3718,12 @@
         <v/>
       </c>
       <c r="G44" s="5">
-        <f>E44*F44</f>
+        <f>ROUND(E44*F44,2)</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="33" customHeight="1">
-      <c r="A45" s="26" t="n"/>
+      <c r="A45" s="25" t="n"/>
       <c r="B45" s="22" t="inlineStr">
         <is>
           <t>35.190.1100 (montaj)</t>
@@ -3667,33 +3747,91 @@
         <v/>
       </c>
       <c r="G45" s="5">
-        <f>E45*F45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="11" t="n"/>
-      <c r="B46" s="11" t="n"/>
-      <c r="C46" s="27" t="inlineStr">
+        <f>ROUND(E45*F45,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="33" customHeight="1">
+      <c r="A46" s="25" t="n"/>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="F46" s="24">
+        <f>IFERROR(VLOOKUP($B46,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G46" s="5">
+        <f>ROUND(E46*F46,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="33" customHeight="1">
+      <c r="A47" s="26" t="n"/>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="F47" s="24">
+        <f>IFERROR(VLOOKUP($B47,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G47" s="5">
+        <f>ROUND(E47*F47,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="n"/>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D46" s="11" t="n"/>
-      <c r="E46" s="11" t="n"/>
-      <c r="F46" s="11" t="n"/>
-      <c r="G46" s="13">
-        <f>SUM(G6:G45)</f>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="11" t="n"/>
+      <c r="G48" s="13">
+        <f>SUM(G6:G47)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A29:A47"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A29:A45"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
@@ -3710,7 +3848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3802,7 +3940,7 @@
         <v/>
       </c>
       <c r="G6" s="5">
-        <f>E6*F6</f>
+        <f>ROUND(E6*F6,2)</f>
         <v/>
       </c>
     </row>
@@ -3835,7 +3973,7 @@
         <v/>
       </c>
       <c r="G7" s="5">
-        <f>E7*F7</f>
+        <f>ROUND(E7*F7,2)</f>
         <v/>
       </c>
     </row>
@@ -3868,7 +4006,7 @@
         <v/>
       </c>
       <c r="G8" s="5">
-        <f>E8*F8</f>
+        <f>ROUND(E8*F8,2)</f>
         <v/>
       </c>
     </row>
@@ -3901,7 +4039,7 @@
         <v/>
       </c>
       <c r="G9" s="5">
-        <f>E9*F9</f>
+        <f>ROUND(E9*F9,2)</f>
         <v/>
       </c>
     </row>
@@ -3934,7 +4072,7 @@
         <v/>
       </c>
       <c r="G10" s="5">
-        <f>E10*F10</f>
+        <f>ROUND(E10*F10,2)</f>
         <v/>
       </c>
     </row>
@@ -3963,7 +4101,7 @@
         <v/>
       </c>
       <c r="G11" s="5">
-        <f>E11*F11</f>
+        <f>ROUND(E11*F11,2)</f>
         <v/>
       </c>
     </row>
@@ -3992,7 +4130,7 @@
         <v/>
       </c>
       <c r="G12" s="5">
-        <f>E12*F12</f>
+        <f>ROUND(E12*F12,2)</f>
         <v/>
       </c>
     </row>
@@ -4025,7 +4163,7 @@
         <v/>
       </c>
       <c r="G13" s="5">
-        <f>E13*F13</f>
+        <f>ROUND(E13*F13,2)</f>
         <v/>
       </c>
     </row>
@@ -4054,7 +4192,7 @@
         <v/>
       </c>
       <c r="G14" s="5">
-        <f>E14*F14</f>
+        <f>ROUND(E14*F14,2)</f>
         <v/>
       </c>
     </row>
@@ -4087,7 +4225,7 @@
         <v/>
       </c>
       <c r="G15" s="5">
-        <f>E15*F15</f>
+        <f>ROUND(E15*F15,2)</f>
         <v/>
       </c>
     </row>
@@ -4116,7 +4254,7 @@
         <v/>
       </c>
       <c r="G16" s="5">
-        <f>E16*F16</f>
+        <f>ROUND(E16*F16,2)</f>
         <v/>
       </c>
     </row>
@@ -4145,7 +4283,7 @@
         <v/>
       </c>
       <c r="G17" s="5">
-        <f>E17*F17</f>
+        <f>ROUND(E17*F17,2)</f>
         <v/>
       </c>
     </row>
@@ -4178,7 +4316,7 @@
         <v/>
       </c>
       <c r="G18" s="5">
-        <f>E18*F18</f>
+        <f>ROUND(E18*F18,2)</f>
         <v/>
       </c>
     </row>
@@ -4207,7 +4345,7 @@
         <v/>
       </c>
       <c r="G19" s="5">
-        <f>E19*F19</f>
+        <f>ROUND(E19*F19,2)</f>
         <v/>
       </c>
     </row>
@@ -4240,7 +4378,7 @@
         <v/>
       </c>
       <c r="G20" s="5">
-        <f>E20*F20</f>
+        <f>ROUND(E20*F20,2)</f>
         <v/>
       </c>
     </row>
@@ -4269,7 +4407,7 @@
         <v/>
       </c>
       <c r="G21" s="5">
-        <f>E21*F21</f>
+        <f>ROUND(E21*F21,2)</f>
         <v/>
       </c>
     </row>
@@ -4298,7 +4436,7 @@
         <v/>
       </c>
       <c r="G22" s="5">
-        <f>E22*F22</f>
+        <f>ROUND(E22*F22,2)</f>
         <v/>
       </c>
     </row>
@@ -4331,7 +4469,7 @@
         <v/>
       </c>
       <c r="G23" s="5">
-        <f>E23*F23</f>
+        <f>ROUND(E23*F23,2)</f>
         <v/>
       </c>
     </row>
@@ -4360,7 +4498,7 @@
         <v/>
       </c>
       <c r="G24" s="5">
-        <f>E24*F24</f>
+        <f>ROUND(E24*F24,2)</f>
         <v/>
       </c>
     </row>
@@ -4393,7 +4531,7 @@
         <v/>
       </c>
       <c r="G25" s="5">
-        <f>E25*F25</f>
+        <f>ROUND(E25*F25,2)</f>
         <v/>
       </c>
     </row>
@@ -4422,7 +4560,7 @@
         <v/>
       </c>
       <c r="G26" s="5">
-        <f>E26*F26</f>
+        <f>ROUND(E26*F26,2)</f>
         <v/>
       </c>
     </row>
@@ -4455,7 +4593,7 @@
         <v/>
       </c>
       <c r="G27" s="5">
-        <f>E27*F27</f>
+        <f>ROUND(E27*F27,2)</f>
         <v/>
       </c>
     </row>
@@ -4488,7 +4626,7 @@
         <v/>
       </c>
       <c r="G28" s="5">
-        <f>E28*F28</f>
+        <f>ROUND(E28*F28,2)</f>
         <v/>
       </c>
     </row>
@@ -4521,7 +4659,7 @@
         <v/>
       </c>
       <c r="G29" s="5">
-        <f>E29*F29</f>
+        <f>ROUND(E29*F29,2)</f>
         <v/>
       </c>
     </row>
@@ -4550,7 +4688,7 @@
         <v/>
       </c>
       <c r="G30" s="5">
-        <f>E30*F30</f>
+        <f>ROUND(E30*F30,2)</f>
         <v/>
       </c>
     </row>
@@ -4579,7 +4717,7 @@
         <v/>
       </c>
       <c r="G31" s="5">
-        <f>E31*F31</f>
+        <f>ROUND(E31*F31,2)</f>
         <v/>
       </c>
     </row>
@@ -4608,7 +4746,7 @@
         <v/>
       </c>
       <c r="G32" s="5">
-        <f>E32*F32</f>
+        <f>ROUND(E32*F32,2)</f>
         <v/>
       </c>
     </row>
@@ -4637,7 +4775,7 @@
         <v/>
       </c>
       <c r="G33" s="5">
-        <f>E33*F33</f>
+        <f>ROUND(E33*F33,2)</f>
         <v/>
       </c>
     </row>
@@ -4666,7 +4804,7 @@
         <v/>
       </c>
       <c r="G34" s="5">
-        <f>E34*F34</f>
+        <f>ROUND(E34*F34,2)</f>
         <v/>
       </c>
     </row>
@@ -4695,7 +4833,7 @@
         <v/>
       </c>
       <c r="G35" s="5">
-        <f>E35*F35</f>
+        <f>ROUND(E35*F35,2)</f>
         <v/>
       </c>
     </row>
@@ -4724,7 +4862,7 @@
         <v/>
       </c>
       <c r="G36" s="5">
-        <f>E36*F36</f>
+        <f>ROUND(E36*F36,2)</f>
         <v/>
       </c>
     </row>
@@ -4753,7 +4891,7 @@
         <v/>
       </c>
       <c r="G37" s="5">
-        <f>E37*F37</f>
+        <f>ROUND(E37*F37,2)</f>
         <v/>
       </c>
     </row>
@@ -4782,7 +4920,7 @@
         <v/>
       </c>
       <c r="G38" s="5">
-        <f>E38*F38</f>
+        <f>ROUND(E38*F38,2)</f>
         <v/>
       </c>
     </row>
@@ -4811,7 +4949,7 @@
         <v/>
       </c>
       <c r="G39" s="5">
-        <f>E39*F39</f>
+        <f>ROUND(E39*F39,2)</f>
         <v/>
       </c>
     </row>
@@ -4840,7 +4978,7 @@
         <v/>
       </c>
       <c r="G40" s="5">
-        <f>E40*F40</f>
+        <f>ROUND(E40*F40,2)</f>
         <v/>
       </c>
     </row>
@@ -4869,7 +5007,7 @@
         <v/>
       </c>
       <c r="G41" s="5">
-        <f>E41*F41</f>
+        <f>ROUND(E41*F41,2)</f>
         <v/>
       </c>
     </row>
@@ -4898,7 +5036,7 @@
         <v/>
       </c>
       <c r="G42" s="5">
-        <f>E42*F42</f>
+        <f>ROUND(E42*F42,2)</f>
         <v/>
       </c>
     </row>
@@ -4927,7 +5065,7 @@
         <v/>
       </c>
       <c r="G43" s="5">
-        <f>E43*F43</f>
+        <f>ROUND(E43*F43,2)</f>
         <v/>
       </c>
     </row>
@@ -4956,12 +5094,12 @@
         <v/>
       </c>
       <c r="G44" s="5">
-        <f>E44*F44</f>
+        <f>ROUND(E44*F44,2)</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="33" customHeight="1">
-      <c r="A45" s="26" t="n"/>
+      <c r="A45" s="25" t="n"/>
       <c r="B45" s="22" t="inlineStr">
         <is>
           <t>35.190.1100 (montaj)</t>
@@ -4985,33 +5123,91 @@
         <v/>
       </c>
       <c r="G45" s="5">
-        <f>E45*F45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="11" t="n"/>
-      <c r="B46" s="11" t="n"/>
-      <c r="C46" s="27" t="inlineStr">
+        <f>ROUND(E45*F45,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="33" customHeight="1">
+      <c r="A46" s="25" t="n"/>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="F46" s="24">
+        <f>IFERROR(VLOOKUP($B46,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G46" s="5">
+        <f>ROUND(E46*F46,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="33" customHeight="1">
+      <c r="A47" s="26" t="n"/>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="F47" s="24">
+        <f>IFERROR(VLOOKUP($B47,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G47" s="5">
+        <f>ROUND(E47*F47,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="n"/>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D46" s="11" t="n"/>
-      <c r="E46" s="11" t="n"/>
-      <c r="F46" s="11" t="n"/>
-      <c r="G46" s="13">
-        <f>SUM(G6:G45)</f>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="11" t="n"/>
+      <c r="G48" s="13">
+        <f>SUM(G6:G47)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A29:A47"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A29:A45"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="C4" s="5">
-        <f>'01 Kümes A Blok'!$G$48</f>
+        <f>'01 Kümes A Blok'!$G$44</f>
         <v/>
       </c>
       <c r="D4" s="6">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>'02 Kümes B Blok'!$G$48</f>
+        <f>'02 Kümes B Blok'!$G$44</f>
         <v/>
       </c>
       <c r="D5" s="6">
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2100,25 +2100,25 @@
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>35.190.1100</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>237.4</v>
+        <v>393.69</v>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F39" s="20">
@@ -2134,18 +2134,18 @@
         <v/>
       </c>
       <c r="I39" s="13" t="n">
-        <v>199.42</v>
-      </c>
-    </row>
-    <row r="40" ht="33" customHeight="1">
+        <v>330.7</v>
+      </c>
+    </row>
+    <row r="40" ht="14" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>35.190.1100 (montaj)</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2154,11 +2154,11 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>46.09</v>
+        <v>271.25</v>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 35.190.1100 pozunun 01.06.2026 tarihli MONTAJ fiyatı 46,09 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 189,92 x 1,25 + montaj 46,09 = 283,49 TL</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F40" s="20">
@@ -2174,31 +2174,31 @@
         <v/>
       </c>
       <c r="I40" s="13" t="n">
-        <v>38.72</v>
+        <v>227.85</v>
       </c>
     </row>
     <row r="41" ht="33" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>35.190.1101</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>193.3</v>
+        <v>1035.88</v>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F41" s="20">
@@ -2214,31 +2214,31 @@
         <v/>
       </c>
       <c r="I41" s="13" t="n">
-        <v>162.37</v>
+        <v>870.14</v>
       </c>
     </row>
     <row r="42" ht="33" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>35.190.1101 (montaj)</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>25.36</v>
+        <v>3199.68</v>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 35.190.1101 pozunun 01.06.2026 tarihli MONTAJ fiyatı 25,36 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 154,64 x 1,25 + montaj 25,36 = 218,66 TL</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F42" s="20">
@@ -2254,27 +2254,27 @@
         <v/>
       </c>
       <c r="I42" s="13" t="n">
-        <v>21.3</v>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
+        <v>2687.73</v>
+      </c>
+    </row>
+    <row r="43" ht="44" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>393.69</v>
+        <v>835.1</v>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
@@ -2294,166 +2294,6 @@
         <v/>
       </c>
       <c r="I43" s="13" t="n">
-        <v>330.7</v>
-      </c>
-    </row>
-    <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0115</t>
-        </is>
-      </c>
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>271.25</v>
-      </c>
-      <c r="E44" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F44" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G44" s="5">
-        <f>D44*(1-F44)</f>
-        <v/>
-      </c>
-      <c r="H44" s="5">
-        <f>D44*$D$3</f>
-        <v/>
-      </c>
-      <c r="I44" s="13" t="n">
-        <v>227.85</v>
-      </c>
-    </row>
-    <row r="45" ht="33" customHeight="1">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0151</t>
-        </is>
-      </c>
-      <c r="B45" s="18" t="inlineStr">
-        <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>1035.88</v>
-      </c>
-      <c r="E45" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F45" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G45" s="5">
-        <f>D45*(1-F45)</f>
-        <v/>
-      </c>
-      <c r="H45" s="5">
-        <f>D45*$D$3</f>
-        <v/>
-      </c>
-      <c r="I45" s="13" t="n">
-        <v>870.14</v>
-      </c>
-    </row>
-    <row r="46" ht="33" customHeight="1">
-      <c r="A46" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0175</t>
-        </is>
-      </c>
-      <c r="B46" s="18" t="inlineStr">
-        <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>3199.68</v>
-      </c>
-      <c r="E46" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F46" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G46" s="5">
-        <f>D46*(1-F46)</f>
-        <v/>
-      </c>
-      <c r="H46" s="5">
-        <f>D46*$D$3</f>
-        <v/>
-      </c>
-      <c r="I46" s="13" t="n">
-        <v>2687.73</v>
-      </c>
-    </row>
-    <row r="47" ht="44" customHeight="1">
-      <c r="A47" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0177</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="inlineStr">
-        <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>835.1</v>
-      </c>
-      <c r="E47" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F47" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G47" s="5">
-        <f>D47*(1-F47)</f>
-        <v/>
-      </c>
-      <c r="H47" s="5">
-        <f>D47*$D$3</f>
-        <v/>
-      </c>
-      <c r="I47" s="13" t="n">
         <v>701.48</v>
       </c>
     </row>
@@ -2472,7 +2312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3665,7 +3505,7 @@
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="25" t="n"/>
+      <c r="A43" s="26" t="n"/>
       <c r="B43" s="22" t="inlineStr">
         <is>
           <t>30.740.5406</t>
@@ -3693,142 +3533,26 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="25" t="n"/>
-      <c r="B44" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1100</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E44" s="23" t="n">
-        <v>502</v>
-      </c>
-      <c r="F44" s="24">
-        <f>IFERROR(VLOOKUP($B44,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G44" s="5">
-        <f>ROUND(E44*F44,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="33" customHeight="1">
-      <c r="A45" s="25" t="n"/>
-      <c r="B45" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E45" s="23" t="n">
-        <v>502</v>
-      </c>
-      <c r="F45" s="24">
-        <f>IFERROR(VLOOKUP($B45,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G45" s="5">
-        <f>ROUND(E45*F45,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="33" customHeight="1">
-      <c r="A46" s="25" t="n"/>
-      <c r="B46" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1101</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E46" s="23" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="F46" s="24">
-        <f>IFERROR(VLOOKUP($B46,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G46" s="5">
-        <f>ROUND(E46*F46,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="33" customHeight="1">
-      <c r="A47" s="26" t="n"/>
-      <c r="B47" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="F47" s="24">
-        <f>IFERROR(VLOOKUP($B47,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G47" s="5">
-        <f>ROUND(E47*F47,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="11" t="n"/>
-      <c r="B48" s="11" t="n"/>
-      <c r="C48" s="27" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="11" t="n"/>
-      <c r="F48" s="11" t="n"/>
-      <c r="G48" s="13">
-        <f>SUM(G6:G47)</f>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="13">
+        <f>SUM(G6:G43)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A29:A47"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A29:A43"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
@@ -3848,7 +3572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5041,7 +4765,7 @@
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="25" t="n"/>
+      <c r="A43" s="26" t="n"/>
       <c r="B43" s="22" t="inlineStr">
         <is>
           <t>30.740.5406</t>
@@ -5069,142 +4793,26 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="25" t="n"/>
-      <c r="B44" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1100</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E44" s="23" t="n">
-        <v>502</v>
-      </c>
-      <c r="F44" s="24">
-        <f>IFERROR(VLOOKUP($B44,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G44" s="5">
-        <f>ROUND(E44*F44,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="33" customHeight="1">
-      <c r="A45" s="25" t="n"/>
-      <c r="B45" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E45" s="23" t="n">
-        <v>502</v>
-      </c>
-      <c r="F45" s="24">
-        <f>IFERROR(VLOOKUP($B45,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G45" s="5">
-        <f>ROUND(E45*F45,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="33" customHeight="1">
-      <c r="A46" s="25" t="n"/>
-      <c r="B46" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1101</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E46" s="23" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="F46" s="24">
-        <f>IFERROR(VLOOKUP($B46,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G46" s="5">
-        <f>ROUND(E46*F46,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="33" customHeight="1">
-      <c r="A47" s="26" t="n"/>
-      <c r="B47" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="F47" s="24">
-        <f>IFERROR(VLOOKUP($B47,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G47" s="5">
-        <f>ROUND(E47*F47,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="11" t="n"/>
-      <c r="B48" s="11" t="n"/>
-      <c r="C48" s="27" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="11" t="n"/>
-      <c r="F48" s="11" t="n"/>
-      <c r="G48" s="13">
-        <f>SUM(G6:G47)</f>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="13">
+        <f>SUM(G6:G43)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A29:A47"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A29:A43"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="C4" s="5">
-        <f>'01 Kümes A Blok'!$G$44</f>
+        <f>'01 Kümes A Blok'!$G$49</f>
         <v/>
       </c>
       <c r="D4" s="6">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>'02 Kümes B Blok'!$G$44</f>
+        <f>'02 Kümes B Blok'!$G$49</f>
         <v/>
       </c>
       <c r="D5" s="6">
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1897,24 +1897,24 @@
         <v>1996.08</v>
       </c>
     </row>
-    <row r="34" ht="33" customHeight="1">
+    <row r="34" ht="22" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>30.190.1304</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>556368.2</v>
+        <v>277.71</v>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
@@ -1934,18 +1934,18 @@
         <v/>
       </c>
       <c r="I34" s="13" t="n">
-        <v>467349.29</v>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
+        <v>233.28</v>
+      </c>
+    </row>
+    <row r="35" ht="33" customHeight="1">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>94825.64999999999</v>
+        <v>556368.2</v>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
@@ -1974,18 +1974,18 @@
         <v/>
       </c>
       <c r="I35" s="13" t="n">
-        <v>79653.55</v>
+        <v>467349.29</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.740.5406</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>18566.2</v>
+        <v>94825.64999999999</v>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
@@ -2014,27 +2014,27 @@
         <v/>
       </c>
       <c r="I36" s="13" t="n">
-        <v>15595.61</v>
+        <v>79653.55</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>508</v>
+        <v>18566.2</v>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
@@ -2054,18 +2054,18 @@
         <v/>
       </c>
       <c r="I37" s="13" t="n">
-        <v>426.72</v>
+        <v>15595.61</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>138.05</v>
+        <v>508</v>
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
@@ -2094,18 +2094,18 @@
         <v/>
       </c>
       <c r="I38" s="13" t="n">
-        <v>115.96</v>
+        <v>426.72</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2114,11 +2114,11 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>393.69</v>
+        <v>138.05</v>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F39" s="20">
@@ -2134,18 +2134,18 @@
         <v/>
       </c>
       <c r="I39" s="13" t="n">
-        <v>330.7</v>
-      </c>
-    </row>
-    <row r="40" ht="14" customHeight="1">
+        <v>115.96</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2154,11 +2154,11 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>271.25</v>
+        <v>237.4</v>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F40" s="20">
@@ -2174,31 +2174,31 @@
         <v/>
       </c>
       <c r="I40" s="13" t="n">
-        <v>227.85</v>
+        <v>199.42</v>
       </c>
     </row>
     <row r="41" ht="33" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>35.190.1100 (montaj)</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1035.88</v>
+        <v>46.09</v>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 35.190.1100 pozunun 01.06.2026 tarihli MONTAJ fiyatı 46,09 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 189,92 x 1,25 + montaj 46,09 = 283,49 TL</t>
         </is>
       </c>
       <c r="F41" s="20">
@@ -2214,31 +2214,31 @@
         <v/>
       </c>
       <c r="I41" s="13" t="n">
-        <v>870.14</v>
+        <v>38.72</v>
       </c>
     </row>
     <row r="42" ht="33" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>3199.68</v>
+        <v>193.3</v>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F42" s="20">
@@ -2254,31 +2254,31 @@
         <v/>
       </c>
       <c r="I42" s="13" t="n">
-        <v>2687.73</v>
-      </c>
-    </row>
-    <row r="43" ht="44" customHeight="1">
+        <v>162.37</v>
+      </c>
+    </row>
+    <row r="43" ht="33" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>35.190.1101 (montaj)</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>835.1</v>
+        <v>25.36</v>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 35.190.1101 pozunun 01.06.2026 tarihli MONTAJ fiyatı 25,36 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 154,64 x 1,25 + montaj 25,36 = 218,66 TL</t>
         </is>
       </c>
       <c r="F43" s="20">
@@ -2294,6 +2294,206 @@
         <v/>
       </c>
       <c r="I43" s="13" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>43.527.1001</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>393.69</v>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F44" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G44" s="5">
+        <f>D44*(1-F44)</f>
+        <v/>
+      </c>
+      <c r="H44" s="5">
+        <f>D44*$D$3</f>
+        <v/>
+      </c>
+      <c r="I44" s="13" t="n">
+        <v>330.7</v>
+      </c>
+    </row>
+    <row r="45" ht="14" customHeight="1">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>TKDK-0115</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>271.25</v>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F45" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G45" s="5">
+        <f>D45*(1-F45)</f>
+        <v/>
+      </c>
+      <c r="H45" s="5">
+        <f>D45*$D$3</f>
+        <v/>
+      </c>
+      <c r="I45" s="13" t="n">
+        <v>227.85</v>
+      </c>
+    </row>
+    <row r="46" ht="33" customHeight="1">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>TKDK-0151</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>1035.88</v>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F46" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G46" s="5">
+        <f>D46*(1-F46)</f>
+        <v/>
+      </c>
+      <c r="H46" s="5">
+        <f>D46*$D$3</f>
+        <v/>
+      </c>
+      <c r="I46" s="13" t="n">
+        <v>870.14</v>
+      </c>
+    </row>
+    <row r="47" ht="33" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>TKDK-0175</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>3199.68</v>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F47" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G47" s="5">
+        <f>D47*(1-F47)</f>
+        <v/>
+      </c>
+      <c r="H47" s="5">
+        <f>D47*$D$3</f>
+        <v/>
+      </c>
+      <c r="I47" s="13" t="n">
+        <v>2687.73</v>
+      </c>
+    </row>
+    <row r="48" ht="44" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>TKDK-0177</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>835.1</v>
+      </c>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F48" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G48" s="5">
+        <f>D48*(1-F48)</f>
+        <v/>
+      </c>
+      <c r="H48" s="5">
+        <f>D48*$D$3</f>
+        <v/>
+      </c>
+      <c r="I48" s="13" t="n">
         <v>701.48</v>
       </c>
     </row>
@@ -2312,7 +2512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3505,7 +3705,7 @@
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="26" t="n"/>
+      <c r="A43" s="25" t="n"/>
       <c r="B43" s="22" t="inlineStr">
         <is>
           <t>30.740.5406</t>
@@ -3533,26 +3733,170 @@
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="n"/>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="27" t="inlineStr">
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="25" t="n"/>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="n">
+        <v>502</v>
+      </c>
+      <c r="F44" s="24">
+        <f>IFERROR(VLOOKUP($B44,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G44" s="5">
+        <f>ROUND(E44*F44,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="33" customHeight="1">
+      <c r="A45" s="25" t="n"/>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="n">
+        <v>502</v>
+      </c>
+      <c r="F45" s="24">
+        <f>IFERROR(VLOOKUP($B45,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G45" s="5">
+        <f>ROUND(E45*F45,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="33" customHeight="1">
+      <c r="A46" s="25" t="n"/>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="F46" s="24">
+        <f>IFERROR(VLOOKUP($B46,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G46" s="5">
+        <f>ROUND(E46*F46,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="33" customHeight="1">
+      <c r="A47" s="25" t="n"/>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="F47" s="24">
+        <f>IFERROR(VLOOKUP($B47,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G47" s="5">
+        <f>ROUND(E47*F47,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="26" t="n"/>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>30.190.1304</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E48" s="23" t="n">
+        <v>123</v>
+      </c>
+      <c r="F48" s="24">
+        <f>IFERROR(VLOOKUP($B48,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G48" s="5">
+        <f>ROUND(E48*F48,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="n"/>
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="13">
-        <f>SUM(G6:G43)</f>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="13">
+        <f>SUM(G6:G48)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A29:A43"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
@@ -3560,6 +3904,7 @@
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A29:A48"/>
     <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3572,7 +3917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4765,7 +5110,7 @@
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="26" t="n"/>
+      <c r="A43" s="25" t="n"/>
       <c r="B43" s="22" t="inlineStr">
         <is>
           <t>30.740.5406</t>
@@ -4793,26 +5138,170 @@
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="n"/>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="27" t="inlineStr">
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="25" t="n"/>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="n">
+        <v>502</v>
+      </c>
+      <c r="F44" s="24">
+        <f>IFERROR(VLOOKUP($B44,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G44" s="5">
+        <f>ROUND(E44*F44,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="33" customHeight="1">
+      <c r="A45" s="25" t="n"/>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="n">
+        <v>502</v>
+      </c>
+      <c r="F45" s="24">
+        <f>IFERROR(VLOOKUP($B45,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G45" s="5">
+        <f>ROUND(E45*F45,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="33" customHeight="1">
+      <c r="A46" s="25" t="n"/>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="F46" s="24">
+        <f>IFERROR(VLOOKUP($B46,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G46" s="5">
+        <f>ROUND(E46*F46,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="33" customHeight="1">
+      <c r="A47" s="25" t="n"/>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="F47" s="24">
+        <f>IFERROR(VLOOKUP($B47,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G47" s="5">
+        <f>ROUND(E47*F47,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="26" t="n"/>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>30.190.1304</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E48" s="23" t="n">
+        <v>123</v>
+      </c>
+      <c r="F48" s="24">
+        <f>IFERROR(VLOOKUP($B48,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G48" s="5">
+        <f>ROUND(E48*F48,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="n"/>
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="13">
-        <f>SUM(G6:G43)</f>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="13">
+        <f>SUM(G6:G48)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A29:A43"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
@@ -4820,6 +5309,7 @@
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A29:A48"/>
     <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="E6" s="23" t="n">
-        <v>1684.39</v>
+        <v>1684.385</v>
       </c>
       <c r="F6" s="24">
         <f>IFERROR(VLOOKUP($B6,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="E6" s="23" t="n">
-        <v>1684.38</v>
+        <v>1684.385</v>
       </c>
       <c r="F6" s="24">
         <f>IFERROR(VLOOKUP($B6,'Fiyatlar'!$A:$I,9,FALSE),0)</f>

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="C4" s="5">
-        <f>'01 Kümes A Blok'!$G$49</f>
+        <f>'01 Kümes A Blok'!$G$54</f>
         <v/>
       </c>
       <c r="D4" s="6">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>'02 Kümes B Blok'!$G$49</f>
+        <f>'02 Kümes B Blok'!$G$54</f>
         <v/>
       </c>
       <c r="D5" s="6">
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1500,7 +1500,7 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>35.100.2105</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
@@ -1540,7 +1540,7 @@
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>35.110.1102</t>
         </is>
       </c>
       <c r="B25" s="18" t="inlineStr">
@@ -1580,7 +1580,7 @@
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
@@ -1620,7 +1620,7 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>35.140.1105</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
@@ -1660,7 +1660,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>35.140.3104</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>35.150.1401</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
@@ -1740,7 +1740,7 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>35.150.1402</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
@@ -1780,7 +1780,7 @@
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>35.160.6102</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
@@ -1820,7 +1820,7 @@
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>35.170.1601</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
@@ -1860,7 +1860,7 @@
     <row r="33" ht="33" customHeight="1">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>35.170.1602</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
@@ -1900,21 +1900,21 @@
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>30.190.1304</t>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>277.71</v>
+        <v>237.4</v>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
@@ -1934,31 +1934,31 @@
         <v/>
       </c>
       <c r="I34" s="13" t="n">
-        <v>233.28</v>
+        <v>199.42</v>
       </c>
     </row>
     <row r="35" ht="33" customHeight="1">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>35.190.1100 (montaj)</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>556368.2</v>
+        <v>46.09</v>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
+          <t>ÇŞB 35.190.1100 pozunun 01.06.2026 tarihli MONTAJ fiyatı 46,09 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 189,92 x 1,25 + montaj 46,09 = 283,49 TL</t>
         </is>
       </c>
       <c r="F35" s="20">
@@ -1974,27 +1974,27 @@
         <v/>
       </c>
       <c r="I35" s="13" t="n">
-        <v>467349.29</v>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
+        <v>38.72</v>
+      </c>
+    </row>
+    <row r="36" ht="33" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>94825.64999999999</v>
+        <v>193.3</v>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
@@ -2014,31 +2014,31 @@
         <v/>
       </c>
       <c r="I36" s="13" t="n">
-        <v>79653.55</v>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
+        <v>162.37</v>
+      </c>
+    </row>
+    <row r="37" ht="33" customHeight="1">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>35.190.1101 (montaj)</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>18566.2</v>
+        <v>25.36</v>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
+          <t>ÇŞB 35.190.1101 pozunun 01.06.2026 tarihli MONTAJ fiyatı 25,36 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 154,64 x 1,25 + montaj 25,36 = 218,66 TL</t>
         </is>
       </c>
       <c r="F37" s="20">
@@ -2054,18 +2054,18 @@
         <v/>
       </c>
       <c r="I37" s="13" t="n">
-        <v>15595.61</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>35.190.1304</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>508</v>
+        <v>277.71</v>
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
@@ -2094,27 +2094,27 @@
         <v/>
       </c>
       <c r="I38" s="13" t="n">
-        <v>426.72</v>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
+        <v>233.28</v>
+      </c>
+    </row>
+    <row r="39" ht="33" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>35.740.1106</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>138.05</v>
+        <v>504175</v>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
@@ -2134,31 +2134,31 @@
         <v/>
       </c>
       <c r="I39" s="13" t="n">
-        <v>115.96</v>
+        <v>423507</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>35.190.1100</t>
+          <t>35.740.1106 (montaj)</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubunun montajı — yerine konulması, bağlantıları ve işler hâlde teslimi</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>237.4</v>
+        <v>24847.84</v>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
+          <t>ÇŞB 35.740.1106 pozunun 01.06.2026 tarihli MONTAJ fiyatı 24.847,84 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 403.340,00 x 1,25 + montaj 24.847,84 = 529.022,84 TL</t>
         </is>
       </c>
       <c r="F40" s="20">
@@ -2174,31 +2174,31 @@
         <v/>
       </c>
       <c r="I40" s="13" t="n">
-        <v>199.42</v>
-      </c>
-    </row>
-    <row r="41" ht="33" customHeight="1">
+        <v>20872.19</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>35.190.1100 (montaj)</t>
+          <t>35.740.5406</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>46.09</v>
+        <v>85930</v>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 35.190.1100 pozunun 01.06.2026 tarihli MONTAJ fiyatı 46,09 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 189,92 x 1,25 + montaj 46,09 = 283,49 TL</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F41" s="20">
@@ -2214,31 +2214,31 @@
         <v/>
       </c>
       <c r="I41" s="13" t="n">
-        <v>38.72</v>
-      </c>
-    </row>
-    <row r="42" ht="33" customHeight="1">
+        <v>72181.2</v>
+      </c>
+    </row>
+    <row r="42" ht="14" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>35.190.1101</t>
+          <t>35.740.5406 (montaj)</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabininin montajı</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>193.3</v>
+        <v>7391.38</v>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
+          <t>ÇŞB 35.740.5406 pozunun 01.06.2026 tarihli MONTAJ fiyatı 7.391,38 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 68.744,00 x 1,25 + montaj 7.391,38 = 93.321,38 TL</t>
         </is>
       </c>
       <c r="F42" s="20">
@@ -2254,31 +2254,31 @@
         <v/>
       </c>
       <c r="I42" s="13" t="n">
-        <v>162.37</v>
-      </c>
-    </row>
-    <row r="43" ht="33" customHeight="1">
+        <v>6208.76</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>35.190.1101 (montaj)</t>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>25.36</v>
+        <v>16824.5</v>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 35.190.1101 pozunun 01.06.2026 tarihli MONTAJ fiyatı 25,36 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 154,64 x 1,25 + montaj 25,36 = 218,66 TL</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F43" s="20">
@@ -2294,31 +2294,31 @@
         <v/>
       </c>
       <c r="I43" s="13" t="n">
-        <v>21.3</v>
+        <v>14132.58</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>35.750.1502 (montaj)</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Aktif yakalama ucunun montajı — direk, taşıyıcı ve bağlantı elemanlarıyla yerine konulması</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>393.69</v>
+        <v>2537.5</v>
       </c>
       <c r="E44" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 35.750.1502 pozunun 01.06.2026 tarihli MONTAJ fiyatı 2.537,50 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 13.459,60 x 1,25 + montaj 2.537,50 = 19.362,00 TL</t>
         </is>
       </c>
       <c r="F44" s="20">
@@ -2334,31 +2334,31 @@
         <v/>
       </c>
       <c r="I44" s="13" t="n">
-        <v>330.7</v>
-      </c>
-    </row>
-    <row r="45" ht="14" customHeight="1">
+        <v>2131.5</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
       <c r="A45" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>271.25</v>
+        <v>461.57</v>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F45" s="20">
@@ -2374,31 +2374,31 @@
         <v/>
       </c>
       <c r="I45" s="13" t="n">
-        <v>227.85</v>
-      </c>
-    </row>
-    <row r="46" ht="33" customHeight="1">
+        <v>387.72</v>
+      </c>
+    </row>
+    <row r="46" ht="14" customHeight="1">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>35.750.2001 (montaj)</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatının montajı</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>1035.88</v>
+        <v>75.25</v>
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 35.750.2001 pozunun 01.06.2026 tarihli MONTAJ fiyatı 75,25 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 369,26 x 1,25 + montaj 75,25 = 536,83 TL</t>
         </is>
       </c>
       <c r="F46" s="20">
@@ -2414,31 +2414,31 @@
         <v/>
       </c>
       <c r="I46" s="13" t="n">
-        <v>870.14</v>
-      </c>
-    </row>
-    <row r="47" ht="33" customHeight="1">
+        <v>63.21</v>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>35.750.3002</t>
         </is>
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>3199.68</v>
+        <v>125.44</v>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F47" s="20">
@@ -2454,31 +2454,31 @@
         <v/>
       </c>
       <c r="I47" s="13" t="n">
-        <v>2687.73</v>
-      </c>
-    </row>
-    <row r="48" ht="44" customHeight="1">
+        <v>105.37</v>
+      </c>
+    </row>
+    <row r="48" ht="14" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>35.750.3002 (montaj)</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+          <t>Bina ihata iletkeni tesisatının montajı — temel topraklaması</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>835.1</v>
+        <v>92.31</v>
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+          <t>ÇŞB 35.750.3002 pozunun 01.06.2026 tarihli MONTAJ fiyatı 92,31 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 100,35 x 1,25 + montaj 92,31 = 217,75 TL</t>
         </is>
       </c>
       <c r="F48" s="20">
@@ -2494,6 +2494,206 @@
         <v/>
       </c>
       <c r="I48" s="13" t="n">
+        <v>77.54000000000001</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>43.527.1001</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>393.69</v>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F49" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G49" s="5">
+        <f>D49*(1-F49)</f>
+        <v/>
+      </c>
+      <c r="H49" s="5">
+        <f>D49*$D$3</f>
+        <v/>
+      </c>
+      <c r="I49" s="13" t="n">
+        <v>330.7</v>
+      </c>
+    </row>
+    <row r="50" ht="14" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>TKDK-0115</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>271.25</v>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F50" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G50" s="5">
+        <f>D50*(1-F50)</f>
+        <v/>
+      </c>
+      <c r="H50" s="5">
+        <f>D50*$D$3</f>
+        <v/>
+      </c>
+      <c r="I50" s="13" t="n">
+        <v>227.85</v>
+      </c>
+    </row>
+    <row r="51" ht="33" customHeight="1">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>TKDK-0151</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>1035.88</v>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F51" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G51" s="5">
+        <f>D51*(1-F51)</f>
+        <v/>
+      </c>
+      <c r="H51" s="5">
+        <f>D51*$D$3</f>
+        <v/>
+      </c>
+      <c r="I51" s="13" t="n">
+        <v>870.14</v>
+      </c>
+    </row>
+    <row r="52" ht="33" customHeight="1">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>TKDK-0175</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>3199.68</v>
+      </c>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F52" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G52" s="5">
+        <f>D52*(1-F52)</f>
+        <v/>
+      </c>
+      <c r="H52" s="5">
+        <f>D52*$D$3</f>
+        <v/>
+      </c>
+      <c r="I52" s="13" t="n">
+        <v>2687.73</v>
+      </c>
+    </row>
+    <row r="53" ht="44" customHeight="1">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>TKDK-0177</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>835.1</v>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
+        </is>
+      </c>
+      <c r="F53" s="20">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G53" s="5">
+        <f>D53*(1-F53)</f>
+        <v/>
+      </c>
+      <c r="H53" s="5">
+        <f>D53*$D$3</f>
+        <v/>
+      </c>
+      <c r="I53" s="13" t="n">
         <v>701.48</v>
       </c>
     </row>
@@ -2512,7 +2712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3302,7 +3502,7 @@
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>35.100.2105</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
@@ -3331,7 +3531,7 @@
       <c r="A30" s="25" t="n"/>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>35.110.1102</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
@@ -3360,7 +3560,7 @@
       <c r="A31" s="25" t="n"/>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
@@ -3389,7 +3589,7 @@
       <c r="A32" s="25" t="n"/>
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>35.140.3104</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
@@ -3418,7 +3618,7 @@
       <c r="A33" s="25" t="n"/>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>35.170.1602</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
@@ -3447,7 +3647,7 @@
       <c r="A34" s="25" t="n"/>
       <c r="B34" s="22" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>35.170.1601</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
@@ -3476,7 +3676,7 @@
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>35.160.6102</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
@@ -3505,7 +3705,7 @@
       <c r="A36" s="25" t="n"/>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>35.150.1402</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
@@ -3534,7 +3734,7 @@
       <c r="A37" s="25" t="n"/>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>35.150.1401</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
@@ -3563,7 +3763,7 @@
       <c r="A38" s="25" t="n"/>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>35.140.1105</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
@@ -3592,7 +3792,7 @@
       <c r="A39" s="25" t="n"/>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>35.750.3002</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
@@ -3617,25 +3817,25 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
+    <row r="40" ht="14" customHeight="1">
       <c r="A40" s="25" t="n"/>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>35.750.3002 (montaj)</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatının montajı — temel topraklaması</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E40" s="23" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="F40" s="24">
         <f>IFERROR(VLOOKUP($B40,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3650,21 +3850,21 @@
       <c r="A41" s="25" t="n"/>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F41" s="24">
         <f>IFERROR(VLOOKUP($B41,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3679,12 +3879,12 @@
       <c r="A42" s="25" t="n"/>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>35.750.1502 (montaj)</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucunun montajı — direk, taşıyıcı ve bağlantı elemanlarıyla yerine konulması</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -3704,25 +3904,25 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="14" customHeight="1">
+    <row r="43" ht="22" customHeight="1">
       <c r="A43" s="25" t="n"/>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F43" s="24">
         <f>IFERROR(VLOOKUP($B43,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3733,25 +3933,25 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1">
+    <row r="44" ht="14" customHeight="1">
       <c r="A44" s="25" t="n"/>
       <c r="B44" s="22" t="inlineStr">
         <is>
-          <t>35.190.1100</t>
+          <t>35.750.2001 (montaj)</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatının montajı</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E44" s="23" t="n">
-        <v>502</v>
+        <v>16</v>
       </c>
       <c r="F44" s="24">
         <f>IFERROR(VLOOKUP($B44,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3762,25 +3962,25 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="33" customHeight="1">
+    <row r="45" ht="22" customHeight="1">
       <c r="A45" s="25" t="n"/>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>35.190.1100 (montaj)</t>
+          <t>35.740.1106</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>502</v>
+        <v>1</v>
       </c>
       <c r="F45" s="24">
         <f>IFERROR(VLOOKUP($B45,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3791,25 +3991,25 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="33" customHeight="1">
+    <row r="46" ht="22" customHeight="1">
       <c r="A46" s="25" t="n"/>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>35.190.1101</t>
+          <t>35.740.1106 (montaj)</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubunun montajı — yerine konulması, bağlantıları ve işler hâlde teslimi</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E46" s="23" t="n">
-        <v>361.2</v>
+        <v>1</v>
       </c>
       <c r="F46" s="24">
         <f>IFERROR(VLOOKUP($B46,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3820,25 +4020,25 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="33" customHeight="1">
+    <row r="47" ht="14" customHeight="1">
       <c r="A47" s="25" t="n"/>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>35.190.1101 (montaj)</t>
+          <t>35.740.5406</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>361.2</v>
+        <v>1</v>
       </c>
       <c r="F47" s="24">
         <f>IFERROR(VLOOKUP($B47,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3849,25 +4049,25 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="26" t="n"/>
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="25" t="n"/>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>30.190.1304</t>
+          <t>35.740.5406 (montaj)</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabininin montajı</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E48" s="23" t="n">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="F48" s="24">
         <f>IFERROR(VLOOKUP($B48,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3878,19 +4078,164 @@
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="11" t="n"/>
-      <c r="B49" s="11" t="n"/>
-      <c r="C49" s="27" t="inlineStr">
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="25" t="n"/>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="n">
+        <v>502</v>
+      </c>
+      <c r="F49" s="24">
+        <f>IFERROR(VLOOKUP($B49,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G49" s="5">
+        <f>ROUND(E49*F49,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="33" customHeight="1">
+      <c r="A50" s="25" t="n"/>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E50" s="23" t="n">
+        <v>502</v>
+      </c>
+      <c r="F50" s="24">
+        <f>IFERROR(VLOOKUP($B50,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G50" s="5">
+        <f>ROUND(E50*F50,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="33" customHeight="1">
+      <c r="A51" s="25" t="n"/>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="F51" s="24">
+        <f>IFERROR(VLOOKUP($B51,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G51" s="5">
+        <f>ROUND(E51*F51,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="33" customHeight="1">
+      <c r="A52" s="25" t="n"/>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E52" s="23" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="F52" s="24">
+        <f>IFERROR(VLOOKUP($B52,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G52" s="5">
+        <f>ROUND(E52*F52,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="26" t="n"/>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1304</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E53" s="23" t="n">
+        <v>123</v>
+      </c>
+      <c r="F53" s="24">
+        <f>IFERROR(VLOOKUP($B53,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G53" s="5">
+        <f>ROUND(E53*F53,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="n"/>
+      <c r="B54" s="11" t="n"/>
+      <c r="C54" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D49" s="11" t="n"/>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="11" t="n"/>
-      <c r="G49" s="13">
-        <f>SUM(G6:G48)</f>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="11" t="n"/>
+      <c r="F54" s="11" t="n"/>
+      <c r="G54" s="13">
+        <f>SUM(G6:G53)</f>
         <v/>
       </c>
     </row>
@@ -3904,7 +4249,7 @@
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A29:A48"/>
+    <mergeCell ref="A29:A53"/>
     <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3917,7 +4262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4707,7 +5052,7 @@
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>35.100.2105</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
@@ -4736,7 +5081,7 @@
       <c r="A30" s="25" t="n"/>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>35.110.1102</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
@@ -4765,7 +5110,7 @@
       <c r="A31" s="25" t="n"/>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
@@ -4794,7 +5139,7 @@
       <c r="A32" s="25" t="n"/>
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>35.140.3104</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
@@ -4823,7 +5168,7 @@
       <c r="A33" s="25" t="n"/>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>35.170.1602</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
@@ -4852,7 +5197,7 @@
       <c r="A34" s="25" t="n"/>
       <c r="B34" s="22" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>35.170.1601</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
@@ -4881,7 +5226,7 @@
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>35.160.6102</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
@@ -4910,7 +5255,7 @@
       <c r="A36" s="25" t="n"/>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>35.150.1402</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
@@ -4939,7 +5284,7 @@
       <c r="A37" s="25" t="n"/>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>35.150.1401</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
@@ -4968,7 +5313,7 @@
       <c r="A38" s="25" t="n"/>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>35.140.1105</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
@@ -4997,7 +5342,7 @@
       <c r="A39" s="25" t="n"/>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>35.750.3002</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
@@ -5022,25 +5367,25 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
+    <row r="40" ht="14" customHeight="1">
       <c r="A40" s="25" t="n"/>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>35.750.3002 (montaj)</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatının montajı — temel topraklaması</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E40" s="23" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="F40" s="24">
         <f>IFERROR(VLOOKUP($B40,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5055,21 +5400,21 @@
       <c r="A41" s="25" t="n"/>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F41" s="24">
         <f>IFERROR(VLOOKUP($B41,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5084,12 +5429,12 @@
       <c r="A42" s="25" t="n"/>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>35.750.1502 (montaj)</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucunun montajı — direk, taşıyıcı ve bağlantı elemanlarıyla yerine konulması</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -5109,25 +5454,25 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="14" customHeight="1">
+    <row r="43" ht="22" customHeight="1">
       <c r="A43" s="25" t="n"/>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F43" s="24">
         <f>IFERROR(VLOOKUP($B43,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5138,25 +5483,25 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1">
+    <row r="44" ht="14" customHeight="1">
       <c r="A44" s="25" t="n"/>
       <c r="B44" s="22" t="inlineStr">
         <is>
-          <t>35.190.1100</t>
+          <t>35.750.2001 (montaj)</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatının montajı</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E44" s="23" t="n">
-        <v>502</v>
+        <v>16</v>
       </c>
       <c r="F44" s="24">
         <f>IFERROR(VLOOKUP($B44,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5167,25 +5512,25 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="33" customHeight="1">
+    <row r="45" ht="22" customHeight="1">
       <c r="A45" s="25" t="n"/>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>35.190.1100 (montaj)</t>
+          <t>35.740.1106</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>502</v>
+        <v>1</v>
       </c>
       <c r="F45" s="24">
         <f>IFERROR(VLOOKUP($B45,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5196,25 +5541,25 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="33" customHeight="1">
+    <row r="46" ht="22" customHeight="1">
       <c r="A46" s="25" t="n"/>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>35.190.1101</t>
+          <t>35.740.1106 (montaj)</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubunun montajı — yerine konulması, bağlantıları ve işler hâlde teslimi</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E46" s="23" t="n">
-        <v>361.2</v>
+        <v>1</v>
       </c>
       <c r="F46" s="24">
         <f>IFERROR(VLOOKUP($B46,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5225,25 +5570,25 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="33" customHeight="1">
+    <row r="47" ht="14" customHeight="1">
       <c r="A47" s="25" t="n"/>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>35.190.1101 (montaj)</t>
+          <t>35.740.5406</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>361.2</v>
+        <v>1</v>
       </c>
       <c r="F47" s="24">
         <f>IFERROR(VLOOKUP($B47,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5254,25 +5599,25 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="26" t="n"/>
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="25" t="n"/>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>30.190.1304</t>
+          <t>35.740.5406 (montaj)</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabininin montajı</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E48" s="23" t="n">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="F48" s="24">
         <f>IFERROR(VLOOKUP($B48,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5283,19 +5628,164 @@
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="11" t="n"/>
-      <c r="B49" s="11" t="n"/>
-      <c r="C49" s="27" t="inlineStr">
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="25" t="n"/>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="n">
+        <v>502</v>
+      </c>
+      <c r="F49" s="24">
+        <f>IFERROR(VLOOKUP($B49,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G49" s="5">
+        <f>ROUND(E49*F49,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="33" customHeight="1">
+      <c r="A50" s="25" t="n"/>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E50" s="23" t="n">
+        <v>502</v>
+      </c>
+      <c r="F50" s="24">
+        <f>IFERROR(VLOOKUP($B50,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G50" s="5">
+        <f>ROUND(E50*F50,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="33" customHeight="1">
+      <c r="A51" s="25" t="n"/>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="F51" s="24">
+        <f>IFERROR(VLOOKUP($B51,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G51" s="5">
+        <f>ROUND(E51*F51,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="33" customHeight="1">
+      <c r="A52" s="25" t="n"/>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E52" s="23" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="F52" s="24">
+        <f>IFERROR(VLOOKUP($B52,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G52" s="5">
+        <f>ROUND(E52*F52,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="26" t="n"/>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>35.190.1304</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E53" s="23" t="n">
+        <v>123</v>
+      </c>
+      <c r="F53" s="24">
+        <f>IFERROR(VLOOKUP($B53,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G53" s="5">
+        <f>ROUND(E53*F53,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="n"/>
+      <c r="B54" s="11" t="n"/>
+      <c r="C54" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D49" s="11" t="n"/>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="11" t="n"/>
-      <c r="G49" s="13">
-        <f>SUM(G6:G48)</f>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="11" t="n"/>
+      <c r="F54" s="11" t="n"/>
+      <c r="G54" s="13">
+        <f>SUM(G6:G53)</f>
         <v/>
       </c>
     </row>
@@ -5309,7 +5799,7 @@
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A29:A48"/>
+    <mergeCell ref="A29:A53"/>
     <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="C4" s="5">
-        <f>'01 Kümes A Blok'!$G$54</f>
+        <f>'01 Kümes A Blok'!$G$49</f>
         <v/>
       </c>
       <c r="D4" s="6">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>'02 Kümes B Blok'!$G$54</f>
+        <f>'02 Kümes B Blok'!$G$49</f>
         <v/>
       </c>
       <c r="D5" s="6">
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>504175</v>
+        <v>556368.2</v>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
@@ -2134,18 +2134,18 @@
         <v/>
       </c>
       <c r="I39" s="13" t="n">
-        <v>423507</v>
+        <v>467349.29</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>35.740.1106 (montaj)</t>
+          <t>35.740.5406</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubunun montajı — yerine konulması, bağlantıları ve işler hâlde teslimi</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2154,11 +2154,11 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>24847.84</v>
+        <v>94825.64999999999</v>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 35.740.1106 pozunun 01.06.2026 tarihli MONTAJ fiyatı 24.847,84 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 403.340,00 x 1,25 + montaj 24.847,84 = 529.022,84 TL</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F40" s="20">
@@ -2174,18 +2174,18 @@
         <v/>
       </c>
       <c r="I40" s="13" t="n">
-        <v>20872.19</v>
+        <v>79653.55</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>35.740.5406</t>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>85930</v>
+        <v>18566.2</v>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
@@ -2214,31 +2214,31 @@
         <v/>
       </c>
       <c r="I41" s="13" t="n">
-        <v>72181.2</v>
-      </c>
-    </row>
-    <row r="42" ht="14" customHeight="1">
+        <v>15595.61</v>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>35.740.5406 (montaj)</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabininin montajı</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>7391.38</v>
+        <v>508</v>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 35.740.5406 pozunun 01.06.2026 tarihli MONTAJ fiyatı 7.391,38 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 68.744,00 x 1,25 + montaj 7.391,38 = 93.321,38 TL</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F42" s="20">
@@ -2254,27 +2254,27 @@
         <v/>
       </c>
       <c r="I42" s="13" t="n">
-        <v>6208.76</v>
+        <v>426.72</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>35.750.1502</t>
+          <t>35.750.3002</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>16824.5</v>
+        <v>138.05</v>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
@@ -2294,31 +2294,31 @@
         <v/>
       </c>
       <c r="I43" s="13" t="n">
-        <v>14132.58</v>
+        <v>115.96</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>35.750.1502 (montaj)</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucunun montajı — direk, taşıyıcı ve bağlantı elemanlarıyla yerine konulması</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>2537.5</v>
+        <v>393.69</v>
       </c>
       <c r="E44" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 35.750.1502 pozunun 01.06.2026 tarihli MONTAJ fiyatı 2.537,50 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 13.459,60 x 1,25 + montaj 2.537,50 = 19.362,00 TL</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F44" s="20">
@@ -2334,31 +2334,31 @@
         <v/>
       </c>
       <c r="I44" s="13" t="n">
-        <v>2131.5</v>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
+        <v>330.7</v>
+      </c>
+    </row>
+    <row r="45" ht="14" customHeight="1">
       <c r="A45" s="17" t="inlineStr">
         <is>
-          <t>35.750.2001</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>461.57</v>
+        <v>271.25</v>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F45" s="20">
@@ -2374,31 +2374,31 @@
         <v/>
       </c>
       <c r="I45" s="13" t="n">
-        <v>387.72</v>
-      </c>
-    </row>
-    <row r="46" ht="14" customHeight="1">
+        <v>227.85</v>
+      </c>
+    </row>
+    <row r="46" ht="33" customHeight="1">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>35.750.2001 (montaj)</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatının montajı</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>75.25</v>
+        <v>1035.88</v>
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 35.750.2001 pozunun 01.06.2026 tarihli MONTAJ fiyatı 75,25 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 369,26 x 1,25 + montaj 75,25 = 536,83 TL</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F46" s="20">
@@ -2414,31 +2414,31 @@
         <v/>
       </c>
       <c r="I46" s="13" t="n">
-        <v>63.21</v>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
+        <v>870.14</v>
+      </c>
+    </row>
+    <row r="47" ht="33" customHeight="1">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>35.750.3002</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>125.44</v>
+        <v>3199.68</v>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F47" s="20">
@@ -2454,31 +2454,31 @@
         <v/>
       </c>
       <c r="I47" s="13" t="n">
-        <v>105.37</v>
-      </c>
-    </row>
-    <row r="48" ht="14" customHeight="1">
+        <v>2687.73</v>
+      </c>
+    </row>
+    <row r="48" ht="44" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>35.750.3002 (montaj)</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatının montajı — temel topraklaması</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>92.31</v>
+        <v>835.1</v>
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 35.750.3002 pozunun 01.06.2026 tarihli MONTAJ fiyatı 92,31 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 100,35 x 1,25 + montaj 92,31 = 217,75 TL</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F48" s="20">
@@ -2494,206 +2494,6 @@
         <v/>
       </c>
       <c r="I48" s="13" t="n">
-        <v>77.54000000000001</v>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="17" t="inlineStr">
-        <is>
-          <t>43.527.1001</t>
-        </is>
-      </c>
-      <c r="B49" s="18" t="inlineStr">
-        <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>393.69</v>
-      </c>
-      <c r="E49" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F49" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G49" s="5">
-        <f>D49*(1-F49)</f>
-        <v/>
-      </c>
-      <c r="H49" s="5">
-        <f>D49*$D$3</f>
-        <v/>
-      </c>
-      <c r="I49" s="13" t="n">
-        <v>330.7</v>
-      </c>
-    </row>
-    <row r="50" ht="14" customHeight="1">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0115</t>
-        </is>
-      </c>
-      <c r="B50" s="18" t="inlineStr">
-        <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>271.25</v>
-      </c>
-      <c r="E50" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F50" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G50" s="5">
-        <f>D50*(1-F50)</f>
-        <v/>
-      </c>
-      <c r="H50" s="5">
-        <f>D50*$D$3</f>
-        <v/>
-      </c>
-      <c r="I50" s="13" t="n">
-        <v>227.85</v>
-      </c>
-    </row>
-    <row r="51" ht="33" customHeight="1">
-      <c r="A51" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0151</t>
-        </is>
-      </c>
-      <c r="B51" s="18" t="inlineStr">
-        <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>1035.88</v>
-      </c>
-      <c r="E51" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F51" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G51" s="5">
-        <f>D51*(1-F51)</f>
-        <v/>
-      </c>
-      <c r="H51" s="5">
-        <f>D51*$D$3</f>
-        <v/>
-      </c>
-      <c r="I51" s="13" t="n">
-        <v>870.14</v>
-      </c>
-    </row>
-    <row r="52" ht="33" customHeight="1">
-      <c r="A52" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0175</t>
-        </is>
-      </c>
-      <c r="B52" s="18" t="inlineStr">
-        <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>3199.68</v>
-      </c>
-      <c r="E52" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F52" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G52" s="5">
-        <f>D52*(1-F52)</f>
-        <v/>
-      </c>
-      <c r="H52" s="5">
-        <f>D52*$D$3</f>
-        <v/>
-      </c>
-      <c r="I52" s="13" t="n">
-        <v>2687.73</v>
-      </c>
-    </row>
-    <row r="53" ht="44" customHeight="1">
-      <c r="A53" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0177</t>
-        </is>
-      </c>
-      <c r="B53" s="18" t="inlineStr">
-        <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>835.1</v>
-      </c>
-      <c r="E53" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F53" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G53" s="5">
-        <f>D53*(1-F53)</f>
-        <v/>
-      </c>
-      <c r="H53" s="5">
-        <f>D53*$D$3</f>
-        <v/>
-      </c>
-      <c r="I53" s="13" t="n">
         <v>701.48</v>
       </c>
     </row>
@@ -2712,7 +2512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3817,25 +3617,25 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="14" customHeight="1">
+    <row r="40" ht="22" customHeight="1">
       <c r="A40" s="25" t="n"/>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>35.750.3002 (montaj)</t>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatının montajı — temel topraklaması</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E40" s="23" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F40" s="24">
         <f>IFERROR(VLOOKUP($B40,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3850,21 +3650,21 @@
       <c r="A41" s="25" t="n"/>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>35.750.1502</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F41" s="24">
         <f>IFERROR(VLOOKUP($B41,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3879,12 +3679,12 @@
       <c r="A42" s="25" t="n"/>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>35.750.1502 (montaj)</t>
+          <t>35.740.1106</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucunun montajı — direk, taşıyıcı ve bağlantı elemanlarıyla yerine konulması</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -3904,25 +3704,25 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="22" customHeight="1">
+    <row r="43" ht="14" customHeight="1">
       <c r="A43" s="25" t="n"/>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>35.750.2001</t>
+          <t>35.740.5406</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F43" s="24">
         <f>IFERROR(VLOOKUP($B43,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3933,25 +3733,25 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="14" customHeight="1">
+    <row r="44" ht="22" customHeight="1">
       <c r="A44" s="25" t="n"/>
       <c r="B44" s="22" t="inlineStr">
         <is>
-          <t>35.750.2001 (montaj)</t>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatının montajı</t>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E44" s="23" t="n">
-        <v>16</v>
+        <v>502</v>
       </c>
       <c r="F44" s="24">
         <f>IFERROR(VLOOKUP($B44,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3962,25 +3762,25 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="22" customHeight="1">
+    <row r="45" ht="33" customHeight="1">
       <c r="A45" s="25" t="n"/>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>35.740.1106</t>
+          <t>35.190.1100 (montaj)</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>1</v>
+        <v>502</v>
       </c>
       <c r="F45" s="24">
         <f>IFERROR(VLOOKUP($B45,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3991,25 +3791,25 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="22" customHeight="1">
+    <row r="46" ht="33" customHeight="1">
       <c r="A46" s="25" t="n"/>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>35.740.1106 (montaj)</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubunun montajı — yerine konulması, bağlantıları ve işler hâlde teslimi</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E46" s="23" t="n">
-        <v>1</v>
+        <v>361.2</v>
       </c>
       <c r="F46" s="24">
         <f>IFERROR(VLOOKUP($B46,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4020,25 +3820,25 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="14" customHeight="1">
+    <row r="47" ht="33" customHeight="1">
       <c r="A47" s="25" t="n"/>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>35.740.5406</t>
+          <t>35.190.1101 (montaj)</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>1</v>
+        <v>361.2</v>
       </c>
       <c r="F47" s="24">
         <f>IFERROR(VLOOKUP($B47,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4049,25 +3849,25 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="14" customHeight="1">
-      <c r="A48" s="25" t="n"/>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="26" t="n"/>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>35.740.5406 (montaj)</t>
+          <t>35.190.1304</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabininin montajı</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E48" s="23" t="n">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="F48" s="24">
         <f>IFERROR(VLOOKUP($B48,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -4078,164 +3878,19 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="25" t="n"/>
-      <c r="B49" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1100</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="n">
-        <v>502</v>
-      </c>
-      <c r="F49" s="24">
-        <f>IFERROR(VLOOKUP($B49,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G49" s="5">
-        <f>ROUND(E49*F49,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="33" customHeight="1">
-      <c r="A50" s="25" t="n"/>
-      <c r="B50" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E50" s="23" t="n">
-        <v>502</v>
-      </c>
-      <c r="F50" s="24">
-        <f>IFERROR(VLOOKUP($B50,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G50" s="5">
-        <f>ROUND(E50*F50,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="33" customHeight="1">
-      <c r="A51" s="25" t="n"/>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1101</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="F51" s="24">
-        <f>IFERROR(VLOOKUP($B51,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G51" s="5">
-        <f>ROUND(E51*F51,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="33" customHeight="1">
-      <c r="A52" s="25" t="n"/>
-      <c r="B52" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E52" s="23" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="F52" s="24">
-        <f>IFERROR(VLOOKUP($B52,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G52" s="5">
-        <f>ROUND(E52*F52,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="26" t="n"/>
-      <c r="B53" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1304</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="inlineStr">
-        <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E53" s="23" t="n">
-        <v>123</v>
-      </c>
-      <c r="F53" s="24">
-        <f>IFERROR(VLOOKUP($B53,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G53" s="5">
-        <f>ROUND(E53*F53,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="n"/>
-      <c r="B54" s="11" t="n"/>
-      <c r="C54" s="27" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="11" t="n"/>
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D54" s="11" t="n"/>
-      <c r="E54" s="11" t="n"/>
-      <c r="F54" s="11" t="n"/>
-      <c r="G54" s="13">
-        <f>SUM(G6:G53)</f>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="13">
+        <f>SUM(G6:G48)</f>
         <v/>
       </c>
     </row>
@@ -4249,7 +3904,7 @@
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A29:A53"/>
+    <mergeCell ref="A29:A48"/>
     <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4262,7 +3917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5367,25 +5022,25 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="14" customHeight="1">
+    <row r="40" ht="22" customHeight="1">
       <c r="A40" s="25" t="n"/>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>35.750.3002 (montaj)</t>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatının montajı — temel topraklaması</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E40" s="23" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="F40" s="24">
         <f>IFERROR(VLOOKUP($B40,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5400,21 +5055,21 @@
       <c r="A41" s="25" t="n"/>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>35.750.1502</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F41" s="24">
         <f>IFERROR(VLOOKUP($B41,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5429,12 +5084,12 @@
       <c r="A42" s="25" t="n"/>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>35.750.1502 (montaj)</t>
+          <t>35.740.1106</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucunun montajı — direk, taşıyıcı ve bağlantı elemanlarıyla yerine konulması</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -5454,25 +5109,25 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="22" customHeight="1">
+    <row r="43" ht="14" customHeight="1">
       <c r="A43" s="25" t="n"/>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>35.750.2001</t>
+          <t>35.740.5406</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F43" s="24">
         <f>IFERROR(VLOOKUP($B43,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5483,25 +5138,25 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="14" customHeight="1">
+    <row r="44" ht="22" customHeight="1">
       <c r="A44" s="25" t="n"/>
       <c r="B44" s="22" t="inlineStr">
         <is>
-          <t>35.750.2001 (montaj)</t>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatının montajı</t>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E44" s="23" t="n">
-        <v>16</v>
+        <v>502</v>
       </c>
       <c r="F44" s="24">
         <f>IFERROR(VLOOKUP($B44,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5512,25 +5167,25 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="22" customHeight="1">
+    <row r="45" ht="33" customHeight="1">
       <c r="A45" s="25" t="n"/>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>35.740.1106</t>
+          <t>35.190.1100 (montaj)</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>1</v>
+        <v>502</v>
       </c>
       <c r="F45" s="24">
         <f>IFERROR(VLOOKUP($B45,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5541,25 +5196,25 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="22" customHeight="1">
+    <row r="46" ht="33" customHeight="1">
       <c r="A46" s="25" t="n"/>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>35.740.1106 (montaj)</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubunun montajı — yerine konulması, bağlantıları ve işler hâlde teslimi</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E46" s="23" t="n">
-        <v>1</v>
+        <v>361.2</v>
       </c>
       <c r="F46" s="24">
         <f>IFERROR(VLOOKUP($B46,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5570,25 +5225,25 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="14" customHeight="1">
+    <row r="47" ht="33" customHeight="1">
       <c r="A47" s="25" t="n"/>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>35.740.5406</t>
+          <t>35.190.1101 (montaj)</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>1</v>
+        <v>361.2</v>
       </c>
       <c r="F47" s="24">
         <f>IFERROR(VLOOKUP($B47,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5599,25 +5254,25 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="14" customHeight="1">
-      <c r="A48" s="25" t="n"/>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="26" t="n"/>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>35.740.5406 (montaj)</t>
+          <t>35.190.1304</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabininin montajı</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E48" s="23" t="n">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="F48" s="24">
         <f>IFERROR(VLOOKUP($B48,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5628,164 +5283,19 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="25" t="n"/>
-      <c r="B49" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1100</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="n">
-        <v>502</v>
-      </c>
-      <c r="F49" s="24">
-        <f>IFERROR(VLOOKUP($B49,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G49" s="5">
-        <f>ROUND(E49*F49,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="33" customHeight="1">
-      <c r="A50" s="25" t="n"/>
-      <c r="B50" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E50" s="23" t="n">
-        <v>502</v>
-      </c>
-      <c r="F50" s="24">
-        <f>IFERROR(VLOOKUP($B50,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G50" s="5">
-        <f>ROUND(E50*F50,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="33" customHeight="1">
-      <c r="A51" s="25" t="n"/>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1101</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="F51" s="24">
-        <f>IFERROR(VLOOKUP($B51,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G51" s="5">
-        <f>ROUND(E51*F51,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="33" customHeight="1">
-      <c r="A52" s="25" t="n"/>
-      <c r="B52" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E52" s="23" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="F52" s="24">
-        <f>IFERROR(VLOOKUP($B52,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G52" s="5">
-        <f>ROUND(E52*F52,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="26" t="n"/>
-      <c r="B53" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1304</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="inlineStr">
-        <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E53" s="23" t="n">
-        <v>123</v>
-      </c>
-      <c r="F53" s="24">
-        <f>IFERROR(VLOOKUP($B53,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G53" s="5">
-        <f>ROUND(E53*F53,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="n"/>
-      <c r="B54" s="11" t="n"/>
-      <c r="C54" s="27" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="11" t="n"/>
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D54" s="11" t="n"/>
-      <c r="E54" s="11" t="n"/>
-      <c r="F54" s="11" t="n"/>
-      <c r="G54" s="13">
-        <f>SUM(G6:G53)</f>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="13">
+        <f>SUM(G6:G48)</f>
         <v/>
       </c>
     </row>
@@ -5799,7 +5309,7 @@
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A29:A53"/>
+    <mergeCell ref="A29:A48"/>
     <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/belgeler/15_KESIF_OZETLERI.xlsx
+++ b/belgeler/15_KESIF_OZETLERI.xlsx
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="C4" s="5">
-        <f>'01 Kümes A Blok'!$G$49</f>
+        <f>'01 Kümes A Blok'!$G$47</f>
         <v/>
       </c>
       <c r="D4" s="6">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>'02 Kümes B Blok'!$G$49</f>
+        <f>'02 Kümes B Blok'!$G$47</f>
         <v/>
       </c>
       <c r="D5" s="6">
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1940,12 +1940,12 @@
     <row r="35" ht="33" customHeight="1">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>35.190.1100 (montaj)</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -1954,11 +1954,11 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>46.09</v>
+        <v>193.3</v>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 35.190.1100 pozunun 01.06.2026 tarihli MONTAJ fiyatı 46,09 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 189,92 x 1,25 + montaj 46,09 = 283,49 TL</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F35" s="20">
@@ -1974,27 +1974,27 @@
         <v/>
       </c>
       <c r="I35" s="13" t="n">
-        <v>38.72</v>
-      </c>
-    </row>
-    <row r="36" ht="33" customHeight="1">
+        <v>162.37</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>35.190.1101</t>
+          <t>35.190.1304</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>193.3</v>
+        <v>277.71</v>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
@@ -2014,31 +2014,31 @@
         <v/>
       </c>
       <c r="I36" s="13" t="n">
-        <v>162.37</v>
+        <v>233.28</v>
       </c>
     </row>
     <row r="37" ht="33" customHeight="1">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>35.190.1101 (montaj)</t>
+          <t>35.740.1106</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>25.36</v>
+        <v>556368.2</v>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 35.190.1101 pozunun 01.06.2026 tarihli MONTAJ fiyatı 25,36 TL; kitabın kendi rakamıdır, kâr ve genel gider içindedir, ayrıca çarpılmamıştır. Kitabın birim fiyatı = malzeme 154,64 x 1,25 + montaj 25,36 = 218,66 TL</t>
+          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
         </is>
       </c>
       <c r="F37" s="20">
@@ -2054,27 +2054,27 @@
         <v/>
       </c>
       <c r="I37" s="13" t="n">
-        <v>21.3</v>
+        <v>467349.29</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>35.190.1304</t>
+          <t>35.740.5406</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>277.71</v>
+        <v>94825.64999999999</v>
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
@@ -2094,18 +2094,18 @@
         <v/>
       </c>
       <c r="I38" s="13" t="n">
-        <v>233.28</v>
-      </c>
-    </row>
-    <row r="39" ht="33" customHeight="1">
+        <v>79653.55</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>35.740.1106</t>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>556368.2</v>
+        <v>18566.2</v>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
@@ -2134,27 +2134,27 @@
         <v/>
       </c>
       <c r="I39" s="13" t="n">
-        <v>467349.29</v>
+        <v>15595.61</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>35.740.5406</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>94825.64999999999</v>
+        <v>508</v>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
@@ -2174,27 +2174,27 @@
         <v/>
       </c>
       <c r="I40" s="13" t="n">
-        <v>79653.55</v>
+        <v>426.72</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>35.750.1502</t>
+          <t>35.750.3002</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>18566.2</v>
+        <v>138.05</v>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
@@ -2214,18 +2214,18 @@
         <v/>
       </c>
       <c r="I41" s="13" t="n">
-        <v>15595.61</v>
+        <v>115.96</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>35.750.2001</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2234,11 +2234,11 @@
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>508</v>
+        <v>393.69</v>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F42" s="20">
@@ -2254,31 +2254,31 @@
         <v/>
       </c>
       <c r="I42" s="13" t="n">
-        <v>426.72</v>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
+        <v>330.7</v>
+      </c>
+    </row>
+    <row r="43" ht="14" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>35.750.3002</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>138.05</v>
+        <v>271.25</v>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>ÇŞB 2026 Haziran elektrik rayici x 1,25</t>
+          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
         </is>
       </c>
       <c r="F43" s="20">
@@ -2294,27 +2294,27 @@
         <v/>
       </c>
       <c r="I43" s="13" t="n">
-        <v>115.96</v>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
+        <v>227.85</v>
+      </c>
+    </row>
+    <row r="44" ht="33" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>393.69</v>
+        <v>1035.88</v>
       </c>
       <c r="E44" s="19" t="inlineStr">
         <is>
@@ -2334,27 +2334,27 @@
         <v/>
       </c>
       <c r="I44" s="13" t="n">
-        <v>330.7</v>
-      </c>
-    </row>
-    <row r="45" ht="14" customHeight="1">
+        <v>870.14</v>
+      </c>
+    </row>
+    <row r="45" ht="33" customHeight="1">
       <c r="A45" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>271.25</v>
+        <v>3199.68</v>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
@@ -2374,18 +2374,18 @@
         <v/>
       </c>
       <c r="I45" s="13" t="n">
-        <v>227.85</v>
-      </c>
-    </row>
-    <row r="46" ht="33" customHeight="1">
+        <v>2687.73</v>
+      </c>
+    </row>
+    <row r="46" ht="44" customHeight="1">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>1035.88</v>
+        <v>835.1</v>
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
@@ -2414,86 +2414,6 @@
         <v/>
       </c>
       <c r="I46" s="13" t="n">
-        <v>870.14</v>
-      </c>
-    </row>
-    <row r="47" ht="33" customHeight="1">
-      <c r="A47" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0175</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="inlineStr">
-        <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>3199.68</v>
-      </c>
-      <c r="E47" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F47" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G47" s="5">
-        <f>D47*(1-F47)</f>
-        <v/>
-      </c>
-      <c r="H47" s="5">
-        <f>D47*$D$3</f>
-        <v/>
-      </c>
-      <c r="I47" s="13" t="n">
-        <v>2687.73</v>
-      </c>
-    </row>
-    <row r="48" ht="44" customHeight="1">
-      <c r="A48" s="17" t="inlineStr">
-        <is>
-          <t>TKDK-0177</t>
-        </is>
-      </c>
-      <c r="B48" s="18" t="inlineStr">
-        <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>835.1</v>
-      </c>
-      <c r="E48" s="19" t="inlineStr">
-        <is>
-          <t>TKDK 17.02.2026 Özel Poz Tablosu</t>
-        </is>
-      </c>
-      <c r="F48" s="20">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="G48" s="5">
-        <f>D48*(1-F48)</f>
-        <v/>
-      </c>
-      <c r="H48" s="5">
-        <f>D48*$D$3</f>
-        <v/>
-      </c>
-      <c r="I48" s="13" t="n">
         <v>701.48</v>
       </c>
     </row>
@@ -2512,7 +2432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3766,12 +3686,12 @@
       <c r="A45" s="25" t="n"/>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>35.190.1100 (montaj)</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -3780,7 +3700,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>502</v>
+        <v>361.2</v>
       </c>
       <c r="F45" s="24">
         <f>IFERROR(VLOOKUP($B45,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3791,25 +3711,25 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="33" customHeight="1">
-      <c r="A46" s="25" t="n"/>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="26" t="n"/>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>35.190.1101</t>
+          <t>35.190.1304</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E46" s="23" t="n">
-        <v>361.2</v>
+        <v>123</v>
       </c>
       <c r="F46" s="24">
         <f>IFERROR(VLOOKUP($B46,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -3820,77 +3740,19 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="33" customHeight="1">
-      <c r="A47" s="25" t="n"/>
-      <c r="B47" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="F47" s="24">
-        <f>IFERROR(VLOOKUP($B47,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G47" s="5">
-        <f>ROUND(E47*F47,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="26" t="n"/>
-      <c r="B48" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1304</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="inlineStr">
-        <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E48" s="23" t="n">
-        <v>123</v>
-      </c>
-      <c r="F48" s="24">
-        <f>IFERROR(VLOOKUP($B48,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G48" s="5">
-        <f>ROUND(E48*F48,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="n"/>
-      <c r="B49" s="11" t="n"/>
-      <c r="C49" s="27" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="11" t="n"/>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D49" s="11" t="n"/>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="11" t="n"/>
-      <c r="G49" s="13">
-        <f>SUM(G6:G48)</f>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="11" t="n"/>
+      <c r="F47" s="11" t="n"/>
+      <c r="G47" s="13">
+        <f>SUM(G6:G46)</f>
         <v/>
       </c>
     </row>
@@ -3901,10 +3763,10 @@
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A29:A46"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A29:A48"/>
     <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3917,7 +3779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5171,12 +5033,12 @@
       <c r="A45" s="25" t="n"/>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>35.190.1100 (montaj)</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -5185,7 +5047,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>502</v>
+        <v>361.2</v>
       </c>
       <c r="F45" s="24">
         <f>IFERROR(VLOOKUP($B45,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5196,25 +5058,25 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="33" customHeight="1">
-      <c r="A46" s="25" t="n"/>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="26" t="n"/>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>35.190.1101</t>
+          <t>35.190.1304</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E46" s="23" t="n">
-        <v>361.2</v>
+        <v>123</v>
       </c>
       <c r="F46" s="24">
         <f>IFERROR(VLOOKUP($B46,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
@@ -5225,77 +5087,19 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="33" customHeight="1">
-      <c r="A47" s="25" t="n"/>
-      <c r="B47" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="F47" s="24">
-        <f>IFERROR(VLOOKUP($B47,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G47" s="5">
-        <f>ROUND(E47*F47,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="26" t="n"/>
-      <c r="B48" s="22" t="inlineStr">
-        <is>
-          <t>35.190.1304</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="inlineStr">
-        <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E48" s="23" t="n">
-        <v>123</v>
-      </c>
-      <c r="F48" s="24">
-        <f>IFERROR(VLOOKUP($B48,'Fiyatlar'!$A:$I,9,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="G48" s="5">
-        <f>ROUND(E48*F48,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="n"/>
-      <c r="B49" s="11" t="n"/>
-      <c r="C49" s="27" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="11" t="n"/>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="27" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="D49" s="11" t="n"/>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="11" t="n"/>
-      <c r="G49" s="13">
-        <f>SUM(G6:G48)</f>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="11" t="n"/>
+      <c r="F47" s="11" t="n"/>
+      <c r="G47" s="13">
+        <f>SUM(G6:G46)</f>
         <v/>
       </c>
     </row>
@@ -5306,10 +5110,10 @@
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A29:A46"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A29:A48"/>
     <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
